--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/1500000/Output_8_14.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/1500000/Output_8_14.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>184344.2916995902</v>
+        <v>190819.2539915235</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9171000.570522964</v>
+        <v>9167573.323130395</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22176005.13690202</v>
+        <v>22176453.17582963</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3983353.718573742</v>
+        <v>3983370.55055655</v>
       </c>
     </row>
     <row r="11">
@@ -8667,28 +8667,28 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>100.8636683457816</v>
+        <v>100.9387195582597</v>
       </c>
       <c r="K11" t="n">
-        <v>99.91746411030702</v>
+        <v>100.0299464227919</v>
       </c>
       <c r="L11" t="n">
-        <v>86.68194260817799</v>
+        <v>86.82148686318189</v>
       </c>
       <c r="M11" t="n">
-        <v>64.46103222224738</v>
+        <v>64.61630209323866</v>
       </c>
       <c r="N11" t="n">
-        <v>60.84366661166607</v>
+        <v>61.00144891149961</v>
       </c>
       <c r="O11" t="n">
-        <v>70.92290991414882</v>
+        <v>71.07189926570237</v>
       </c>
       <c r="P11" t="n">
-        <v>95.38055856933971</v>
+        <v>95.50771753390021</v>
       </c>
       <c r="Q11" t="n">
-        <v>120.286167261384</v>
+        <v>120.3816583481039</v>
       </c>
       <c r="R11" t="n">
         <v>65.71641987298243</v>
@@ -8746,28 +8746,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J12" t="n">
-        <v>79.08163610062888</v>
+        <v>79.12633608862856</v>
       </c>
       <c r="K12" t="n">
-        <v>56.21884463473624</v>
+        <v>56.29524403393702</v>
       </c>
       <c r="L12" t="n">
-        <v>28.8027288364778</v>
+        <v>28.90545725697471</v>
       </c>
       <c r="M12" t="n">
-        <v>14.05903392201816</v>
+        <v>14.17891314335149</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>22.33166897274616</v>
+        <v>22.44423757443683</v>
       </c>
       <c r="P12" t="n">
-        <v>37.45148288602822</v>
+        <v>37.54182911310821</v>
       </c>
       <c r="Q12" t="n">
-        <v>75.4587552180969</v>
+        <v>75.5191492782957</v>
       </c>
       <c r="R12" t="n">
         <v>45.52166981132082</v>
@@ -8828,22 +8828,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K13" t="n">
-        <v>79.77883194102714</v>
+        <v>79.82491575659759</v>
       </c>
       <c r="L13" t="n">
-        <v>71.88156152713984</v>
+        <v>71.94053294496764</v>
       </c>
       <c r="M13" t="n">
-        <v>72.49783312793285</v>
+        <v>72.56001021962936</v>
       </c>
       <c r="N13" t="n">
-        <v>62.83710184228225</v>
+        <v>62.89780050171086</v>
       </c>
       <c r="O13" t="n">
-        <v>78.55850566495744</v>
+        <v>78.61457070130248</v>
       </c>
       <c r="P13" t="n">
-        <v>86.47488929504921</v>
+        <v>86.52286261917671</v>
       </c>
       <c r="Q13" t="n">
         <v>65.34295837775146</v>
@@ -8904,28 +8904,28 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>100.8636683457816</v>
+        <v>100.9387195582597</v>
       </c>
       <c r="K14" t="n">
-        <v>99.91746411030702</v>
+        <v>100.0299464227919</v>
       </c>
       <c r="L14" t="n">
-        <v>86.68194260817799</v>
+        <v>86.82148686318189</v>
       </c>
       <c r="M14" t="n">
-        <v>64.46103222224738</v>
+        <v>64.61630209323866</v>
       </c>
       <c r="N14" t="n">
-        <v>60.84366661166607</v>
+        <v>61.00144891149961</v>
       </c>
       <c r="O14" t="n">
-        <v>70.92290991414882</v>
+        <v>71.07189926570237</v>
       </c>
       <c r="P14" t="n">
-        <v>95.38055856933971</v>
+        <v>95.50771753390021</v>
       </c>
       <c r="Q14" t="n">
-        <v>120.286167261384</v>
+        <v>120.3816583481039</v>
       </c>
       <c r="R14" t="n">
         <v>65.71641987298243</v>
@@ -8983,28 +8983,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J15" t="n">
-        <v>79.08163610062888</v>
+        <v>79.12633608862856</v>
       </c>
       <c r="K15" t="n">
-        <v>56.21884463473624</v>
+        <v>56.29524403393702</v>
       </c>
       <c r="L15" t="n">
-        <v>28.8027288364778</v>
+        <v>28.90545725697471</v>
       </c>
       <c r="M15" t="n">
-        <v>14.05903392201816</v>
+        <v>14.17891314335149</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>22.33166897274616</v>
+        <v>22.44423757443683</v>
       </c>
       <c r="P15" t="n">
-        <v>37.45148288602822</v>
+        <v>37.54182911310821</v>
       </c>
       <c r="Q15" t="n">
-        <v>75.4587552180969</v>
+        <v>75.5191492782957</v>
       </c>
       <c r="R15" t="n">
         <v>45.52166981132082</v>
@@ -9065,22 +9065,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K16" t="n">
-        <v>79.77883194102714</v>
+        <v>79.82491575659759</v>
       </c>
       <c r="L16" t="n">
-        <v>71.88156152713984</v>
+        <v>71.94053294496764</v>
       </c>
       <c r="M16" t="n">
-        <v>72.49783312793285</v>
+        <v>72.56001021962936</v>
       </c>
       <c r="N16" t="n">
-        <v>62.83710184228225</v>
+        <v>62.89780050171086</v>
       </c>
       <c r="O16" t="n">
-        <v>78.55850566495744</v>
+        <v>78.61457070130248</v>
       </c>
       <c r="P16" t="n">
-        <v>86.47488929504921</v>
+        <v>86.52286261917671</v>
       </c>
       <c r="Q16" t="n">
         <v>65.34295837775146</v>
@@ -9141,28 +9141,28 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>100.8636683457816</v>
+        <v>100.9387195582597</v>
       </c>
       <c r="K17" t="n">
-        <v>99.91746411030702</v>
+        <v>100.0299464227919</v>
       </c>
       <c r="L17" t="n">
-        <v>86.68194260817799</v>
+        <v>86.82148686318189</v>
       </c>
       <c r="M17" t="n">
-        <v>64.46103222224738</v>
+        <v>64.61630209323866</v>
       </c>
       <c r="N17" t="n">
-        <v>60.84366661166607</v>
+        <v>61.00144891149961</v>
       </c>
       <c r="O17" t="n">
-        <v>70.92290991414882</v>
+        <v>71.07189926570237</v>
       </c>
       <c r="P17" t="n">
-        <v>95.38055856933971</v>
+        <v>95.50771753390021</v>
       </c>
       <c r="Q17" t="n">
-        <v>120.286167261384</v>
+        <v>120.3816583481039</v>
       </c>
       <c r="R17" t="n">
         <v>65.71641987298243</v>
@@ -9220,28 +9220,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J18" t="n">
-        <v>79.08163610062888</v>
+        <v>79.12633608862856</v>
       </c>
       <c r="K18" t="n">
-        <v>56.21884463473624</v>
+        <v>56.29524403393702</v>
       </c>
       <c r="L18" t="n">
-        <v>28.8027288364778</v>
+        <v>28.90545725697471</v>
       </c>
       <c r="M18" t="n">
-        <v>14.05903392201816</v>
+        <v>14.17891314335149</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>22.33166897274616</v>
+        <v>22.44423757443683</v>
       </c>
       <c r="P18" t="n">
-        <v>37.45148288602822</v>
+        <v>37.54182911310821</v>
       </c>
       <c r="Q18" t="n">
-        <v>75.4587552180969</v>
+        <v>75.5191492782957</v>
       </c>
       <c r="R18" t="n">
         <v>45.52166981132082</v>
@@ -9302,22 +9302,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K19" t="n">
-        <v>79.77883194102714</v>
+        <v>79.82491575659759</v>
       </c>
       <c r="L19" t="n">
-        <v>71.88156152713984</v>
+        <v>71.94053294496764</v>
       </c>
       <c r="M19" t="n">
-        <v>72.49783312793285</v>
+        <v>72.56001021962936</v>
       </c>
       <c r="N19" t="n">
-        <v>62.83710184228225</v>
+        <v>62.89780050171086</v>
       </c>
       <c r="O19" t="n">
-        <v>78.55850566495744</v>
+        <v>78.61457070130248</v>
       </c>
       <c r="P19" t="n">
-        <v>86.47488929504921</v>
+        <v>86.52286261917671</v>
       </c>
       <c r="Q19" t="n">
         <v>65.34295837775146</v>
@@ -9378,28 +9378,28 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>100.8636683457816</v>
+        <v>100.9387195582597</v>
       </c>
       <c r="K20" t="n">
-        <v>99.91746411030702</v>
+        <v>100.0299464227919</v>
       </c>
       <c r="L20" t="n">
-        <v>86.68194260817799</v>
+        <v>86.82148686318189</v>
       </c>
       <c r="M20" t="n">
-        <v>64.46103222224738</v>
+        <v>64.61630209323866</v>
       </c>
       <c r="N20" t="n">
-        <v>60.84366661166607</v>
+        <v>61.00144891149961</v>
       </c>
       <c r="O20" t="n">
-        <v>70.92290991414882</v>
+        <v>71.07189926570237</v>
       </c>
       <c r="P20" t="n">
-        <v>95.38055856933971</v>
+        <v>95.50771753390021</v>
       </c>
       <c r="Q20" t="n">
-        <v>120.286167261384</v>
+        <v>120.3816583481039</v>
       </c>
       <c r="R20" t="n">
         <v>65.71641987298243</v>
@@ -9457,28 +9457,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J21" t="n">
-        <v>79.08163610062888</v>
+        <v>79.12633608862856</v>
       </c>
       <c r="K21" t="n">
-        <v>56.21884463473624</v>
+        <v>56.29524403393702</v>
       </c>
       <c r="L21" t="n">
-        <v>28.8027288364778</v>
+        <v>28.90545725697471</v>
       </c>
       <c r="M21" t="n">
-        <v>14.05903392201816</v>
+        <v>14.17891314335149</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>22.33166897274616</v>
+        <v>22.44423757443683</v>
       </c>
       <c r="P21" t="n">
-        <v>37.45148288602822</v>
+        <v>37.54182911310821</v>
       </c>
       <c r="Q21" t="n">
-        <v>75.4587552180969</v>
+        <v>75.5191492782957</v>
       </c>
       <c r="R21" t="n">
         <v>45.52166981132082</v>
@@ -9539,22 +9539,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K22" t="n">
-        <v>79.77883194102714</v>
+        <v>79.82491575659759</v>
       </c>
       <c r="L22" t="n">
-        <v>71.88156152713984</v>
+        <v>71.94053294496764</v>
       </c>
       <c r="M22" t="n">
-        <v>72.49783312793285</v>
+        <v>72.56001021962936</v>
       </c>
       <c r="N22" t="n">
-        <v>62.83710184228225</v>
+        <v>62.89780050171086</v>
       </c>
       <c r="O22" t="n">
-        <v>78.55850566495744</v>
+        <v>78.61457070130248</v>
       </c>
       <c r="P22" t="n">
-        <v>86.47488929504921</v>
+        <v>86.52286261917671</v>
       </c>
       <c r="Q22" t="n">
         <v>65.34295837775146</v>
@@ -9615,28 +9615,28 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>100.8636683457816</v>
+        <v>100.9387195582597</v>
       </c>
       <c r="K23" t="n">
-        <v>99.91746411030702</v>
+        <v>100.0299464227919</v>
       </c>
       <c r="L23" t="n">
-        <v>86.68194260817799</v>
+        <v>86.82148686318189</v>
       </c>
       <c r="M23" t="n">
-        <v>64.46103222224738</v>
+        <v>64.61630209323866</v>
       </c>
       <c r="N23" t="n">
-        <v>60.84366661166607</v>
+        <v>61.00144891149961</v>
       </c>
       <c r="O23" t="n">
-        <v>70.92290991414882</v>
+        <v>71.07189926570237</v>
       </c>
       <c r="P23" t="n">
-        <v>95.38055856933971</v>
+        <v>95.50771753390021</v>
       </c>
       <c r="Q23" t="n">
-        <v>120.286167261384</v>
+        <v>120.3816583481039</v>
       </c>
       <c r="R23" t="n">
         <v>65.71641987298243</v>
@@ -9694,28 +9694,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J24" t="n">
-        <v>79.08163610062888</v>
+        <v>79.12633608862856</v>
       </c>
       <c r="K24" t="n">
-        <v>56.21884463473624</v>
+        <v>56.29524403393702</v>
       </c>
       <c r="L24" t="n">
-        <v>28.8027288364778</v>
+        <v>28.90545725697471</v>
       </c>
       <c r="M24" t="n">
-        <v>14.05903392201816</v>
+        <v>14.17891314335149</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>22.33166897274616</v>
+        <v>22.44423757443683</v>
       </c>
       <c r="P24" t="n">
-        <v>37.45148288602822</v>
+        <v>37.54182911310821</v>
       </c>
       <c r="Q24" t="n">
-        <v>75.4587552180969</v>
+        <v>75.5191492782957</v>
       </c>
       <c r="R24" t="n">
         <v>45.52166981132082</v>
@@ -9776,22 +9776,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K25" t="n">
-        <v>79.77883194102714</v>
+        <v>79.82491575659759</v>
       </c>
       <c r="L25" t="n">
-        <v>71.88156152713984</v>
+        <v>71.94053294496764</v>
       </c>
       <c r="M25" t="n">
-        <v>72.49783312793285</v>
+        <v>72.56001021962936</v>
       </c>
       <c r="N25" t="n">
-        <v>62.83710184228225</v>
+        <v>62.89780050171086</v>
       </c>
       <c r="O25" t="n">
-        <v>78.55850566495744</v>
+        <v>78.61457070130248</v>
       </c>
       <c r="P25" t="n">
-        <v>86.47488929504921</v>
+        <v>86.52286261917671</v>
       </c>
       <c r="Q25" t="n">
         <v>65.34295837775146</v>
@@ -9852,28 +9852,28 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>100.8636683457816</v>
+        <v>100.9387195582597</v>
       </c>
       <c r="K26" t="n">
-        <v>99.91746411030702</v>
+        <v>100.0299464227919</v>
       </c>
       <c r="L26" t="n">
-        <v>86.68194260817799</v>
+        <v>86.82148686318189</v>
       </c>
       <c r="M26" t="n">
-        <v>64.46103222224738</v>
+        <v>64.61630209323866</v>
       </c>
       <c r="N26" t="n">
-        <v>60.84366661166607</v>
+        <v>61.00144891149961</v>
       </c>
       <c r="O26" t="n">
-        <v>70.92290991414882</v>
+        <v>71.07189926570237</v>
       </c>
       <c r="P26" t="n">
-        <v>95.38055856933971</v>
+        <v>95.50771753390021</v>
       </c>
       <c r="Q26" t="n">
-        <v>120.286167261384</v>
+        <v>120.3816583481039</v>
       </c>
       <c r="R26" t="n">
         <v>65.71641987298243</v>
@@ -9931,28 +9931,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J27" t="n">
-        <v>79.08163610062888</v>
+        <v>79.12633608862856</v>
       </c>
       <c r="K27" t="n">
-        <v>56.21884463473624</v>
+        <v>56.29524403393702</v>
       </c>
       <c r="L27" t="n">
-        <v>28.8027288364778</v>
+        <v>28.90545725697471</v>
       </c>
       <c r="M27" t="n">
-        <v>14.05903392201816</v>
+        <v>14.17891314335149</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>22.33166897274616</v>
+        <v>22.44423757443683</v>
       </c>
       <c r="P27" t="n">
-        <v>37.45148288602822</v>
+        <v>37.54182911310821</v>
       </c>
       <c r="Q27" t="n">
-        <v>75.4587552180969</v>
+        <v>75.5191492782957</v>
       </c>
       <c r="R27" t="n">
         <v>45.52166981132082</v>
@@ -10013,22 +10013,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K28" t="n">
-        <v>79.77883194102714</v>
+        <v>79.82491575659759</v>
       </c>
       <c r="L28" t="n">
-        <v>71.88156152713984</v>
+        <v>71.94053294496764</v>
       </c>
       <c r="M28" t="n">
-        <v>72.49783312793285</v>
+        <v>72.56001021962936</v>
       </c>
       <c r="N28" t="n">
-        <v>62.83710184228225</v>
+        <v>62.89780050171086</v>
       </c>
       <c r="O28" t="n">
-        <v>78.55850566495744</v>
+        <v>78.61457070130248</v>
       </c>
       <c r="P28" t="n">
-        <v>86.47488929504921</v>
+        <v>86.52286261917671</v>
       </c>
       <c r="Q28" t="n">
         <v>65.34295837775146</v>
@@ -10089,28 +10089,28 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>100.8636683457816</v>
+        <v>100.9387195582597</v>
       </c>
       <c r="K29" t="n">
-        <v>99.91746411030702</v>
+        <v>100.0299464227919</v>
       </c>
       <c r="L29" t="n">
-        <v>86.68194260817799</v>
+        <v>86.82148686318189</v>
       </c>
       <c r="M29" t="n">
-        <v>64.46103222224738</v>
+        <v>64.61630209323866</v>
       </c>
       <c r="N29" t="n">
-        <v>60.84366661166607</v>
+        <v>61.00144891149961</v>
       </c>
       <c r="O29" t="n">
-        <v>70.92290991414882</v>
+        <v>71.07189926570237</v>
       </c>
       <c r="P29" t="n">
-        <v>95.38055856933971</v>
+        <v>95.50771753390021</v>
       </c>
       <c r="Q29" t="n">
-        <v>120.286167261384</v>
+        <v>120.3816583481039</v>
       </c>
       <c r="R29" t="n">
         <v>65.71641987298243</v>
@@ -10168,28 +10168,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J30" t="n">
-        <v>79.08163610062888</v>
+        <v>79.12633608862856</v>
       </c>
       <c r="K30" t="n">
-        <v>56.21884463473624</v>
+        <v>56.29524403393702</v>
       </c>
       <c r="L30" t="n">
-        <v>28.8027288364778</v>
+        <v>28.90545725697471</v>
       </c>
       <c r="M30" t="n">
-        <v>14.05903392201816</v>
+        <v>14.17891314335149</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>22.33166897274616</v>
+        <v>22.44423757443683</v>
       </c>
       <c r="P30" t="n">
-        <v>37.45148288602822</v>
+        <v>37.54182911310821</v>
       </c>
       <c r="Q30" t="n">
-        <v>75.4587552180969</v>
+        <v>75.5191492782957</v>
       </c>
       <c r="R30" t="n">
         <v>45.52166981132082</v>
@@ -10250,22 +10250,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K31" t="n">
-        <v>79.77883194102714</v>
+        <v>79.82491575659759</v>
       </c>
       <c r="L31" t="n">
-        <v>71.88156152713984</v>
+        <v>71.94053294496764</v>
       </c>
       <c r="M31" t="n">
-        <v>72.49783312793285</v>
+        <v>72.56001021962936</v>
       </c>
       <c r="N31" t="n">
-        <v>62.83710184228225</v>
+        <v>62.89780050171086</v>
       </c>
       <c r="O31" t="n">
-        <v>78.55850566495744</v>
+        <v>78.61457070130248</v>
       </c>
       <c r="P31" t="n">
-        <v>86.47488929504921</v>
+        <v>86.52286261917671</v>
       </c>
       <c r="Q31" t="n">
         <v>65.34295837775146</v>
@@ -10326,28 +10326,28 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>100.8636683457816</v>
+        <v>100.9387195582597</v>
       </c>
       <c r="K32" t="n">
-        <v>99.91746411030702</v>
+        <v>100.0299464227919</v>
       </c>
       <c r="L32" t="n">
-        <v>86.68194260817799</v>
+        <v>86.82148686318186</v>
       </c>
       <c r="M32" t="n">
-        <v>64.46103222224738</v>
+        <v>64.61630209323863</v>
       </c>
       <c r="N32" t="n">
-        <v>60.84366661166607</v>
+        <v>61.00144891149961</v>
       </c>
       <c r="O32" t="n">
-        <v>70.92290991414882</v>
+        <v>71.0718992657024</v>
       </c>
       <c r="P32" t="n">
-        <v>95.38055856933971</v>
+        <v>95.50771753390021</v>
       </c>
       <c r="Q32" t="n">
-        <v>120.286167261384</v>
+        <v>120.3816583481039</v>
       </c>
       <c r="R32" t="n">
         <v>65.71641987298243</v>
@@ -10405,28 +10405,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J33" t="n">
-        <v>79.08163610062888</v>
+        <v>79.12633608862856</v>
       </c>
       <c r="K33" t="n">
-        <v>56.21884463473624</v>
+        <v>56.29524403393702</v>
       </c>
       <c r="L33" t="n">
-        <v>28.8027288364778</v>
+        <v>28.90545725697471</v>
       </c>
       <c r="M33" t="n">
-        <v>14.05903392201816</v>
+        <v>14.17891314335149</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>22.33166897274616</v>
+        <v>22.44423757443683</v>
       </c>
       <c r="P33" t="n">
-        <v>37.45148288602822</v>
+        <v>37.54182911310821</v>
       </c>
       <c r="Q33" t="n">
-        <v>75.4587552180969</v>
+        <v>75.51914927829571</v>
       </c>
       <c r="R33" t="n">
         <v>45.52166981132082</v>
@@ -10487,22 +10487,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K34" t="n">
-        <v>79.77883194102714</v>
+        <v>79.82491575659759</v>
       </c>
       <c r="L34" t="n">
-        <v>71.88156152713984</v>
+        <v>71.94053294496764</v>
       </c>
       <c r="M34" t="n">
-        <v>72.49783312793285</v>
+        <v>72.56001021962938</v>
       </c>
       <c r="N34" t="n">
-        <v>62.83710184228225</v>
+        <v>62.89780050171086</v>
       </c>
       <c r="O34" t="n">
-        <v>78.55850566495744</v>
+        <v>78.61457070130248</v>
       </c>
       <c r="P34" t="n">
-        <v>86.47488929504921</v>
+        <v>86.52286261917671</v>
       </c>
       <c r="Q34" t="n">
         <v>65.34295837775146</v>
@@ -10563,28 +10563,28 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>100.8636683457816</v>
+        <v>100.9387195582597</v>
       </c>
       <c r="K35" t="n">
-        <v>99.91746411030702</v>
+        <v>100.0299464227919</v>
       </c>
       <c r="L35" t="n">
-        <v>86.68194260817799</v>
+        <v>86.82148686318189</v>
       </c>
       <c r="M35" t="n">
-        <v>64.46103222224738</v>
+        <v>64.61630209323866</v>
       </c>
       <c r="N35" t="n">
-        <v>60.84366661166607</v>
+        <v>61.00144891149961</v>
       </c>
       <c r="O35" t="n">
-        <v>70.92290991414882</v>
+        <v>71.07189926570237</v>
       </c>
       <c r="P35" t="n">
-        <v>95.38055856933971</v>
+        <v>95.50771753390021</v>
       </c>
       <c r="Q35" t="n">
-        <v>120.286167261384</v>
+        <v>120.3816583481039</v>
       </c>
       <c r="R35" t="n">
         <v>65.71641987298243</v>
@@ -10642,28 +10642,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J36" t="n">
-        <v>79.08163610062888</v>
+        <v>79.12633608862856</v>
       </c>
       <c r="K36" t="n">
-        <v>56.21884463473624</v>
+        <v>56.29524403393702</v>
       </c>
       <c r="L36" t="n">
-        <v>28.8027288364778</v>
+        <v>28.90545725697471</v>
       </c>
       <c r="M36" t="n">
-        <v>14.05903392201816</v>
+        <v>14.17891314335149</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>22.33166897274616</v>
+        <v>22.44423757443683</v>
       </c>
       <c r="P36" t="n">
-        <v>37.45148288602822</v>
+        <v>37.54182911310821</v>
       </c>
       <c r="Q36" t="n">
-        <v>75.4587552180969</v>
+        <v>75.5191492782957</v>
       </c>
       <c r="R36" t="n">
         <v>45.52166981132082</v>
@@ -10724,22 +10724,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K37" t="n">
-        <v>79.77883194102714</v>
+        <v>79.82491575659759</v>
       </c>
       <c r="L37" t="n">
-        <v>71.88156152713984</v>
+        <v>71.94053294496764</v>
       </c>
       <c r="M37" t="n">
-        <v>72.49783312793285</v>
+        <v>72.56001021962936</v>
       </c>
       <c r="N37" t="n">
-        <v>62.83710184228225</v>
+        <v>62.89780050171086</v>
       </c>
       <c r="O37" t="n">
-        <v>78.55850566495744</v>
+        <v>78.61457070130248</v>
       </c>
       <c r="P37" t="n">
-        <v>86.47488929504921</v>
+        <v>86.52286261917671</v>
       </c>
       <c r="Q37" t="n">
         <v>65.34295837775146</v>
@@ -10800,28 +10800,28 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>100.8636683457816</v>
+        <v>100.9387195582597</v>
       </c>
       <c r="K38" t="n">
-        <v>99.91746411030702</v>
+        <v>100.0299464227919</v>
       </c>
       <c r="L38" t="n">
-        <v>86.68194260817799</v>
+        <v>86.82148686318189</v>
       </c>
       <c r="M38" t="n">
-        <v>64.46103222224738</v>
+        <v>64.61630209323866</v>
       </c>
       <c r="N38" t="n">
-        <v>60.84366661166607</v>
+        <v>61.00144891149961</v>
       </c>
       <c r="O38" t="n">
-        <v>70.92290991414882</v>
+        <v>71.07189926570237</v>
       </c>
       <c r="P38" t="n">
-        <v>95.38055856933971</v>
+        <v>95.50771753390021</v>
       </c>
       <c r="Q38" t="n">
-        <v>120.286167261384</v>
+        <v>120.3816583481039</v>
       </c>
       <c r="R38" t="n">
         <v>65.71641987298243</v>
@@ -10879,28 +10879,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J39" t="n">
-        <v>79.08163610062888</v>
+        <v>79.12633608862856</v>
       </c>
       <c r="K39" t="n">
-        <v>56.21884463473624</v>
+        <v>56.29524403393702</v>
       </c>
       <c r="L39" t="n">
-        <v>28.8027288364778</v>
+        <v>28.90545725697471</v>
       </c>
       <c r="M39" t="n">
-        <v>14.05903392201816</v>
+        <v>14.17891314335149</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>22.33166897274616</v>
+        <v>22.44423757443683</v>
       </c>
       <c r="P39" t="n">
-        <v>37.45148288602822</v>
+        <v>37.54182911310821</v>
       </c>
       <c r="Q39" t="n">
-        <v>75.4587552180969</v>
+        <v>75.5191492782957</v>
       </c>
       <c r="R39" t="n">
         <v>45.52166981132082</v>
@@ -10961,22 +10961,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K40" t="n">
-        <v>79.77883194102714</v>
+        <v>79.82491575659759</v>
       </c>
       <c r="L40" t="n">
-        <v>71.88156152713984</v>
+        <v>71.94053294496764</v>
       </c>
       <c r="M40" t="n">
-        <v>72.49783312793285</v>
+        <v>72.56001021962936</v>
       </c>
       <c r="N40" t="n">
-        <v>62.83710184228225</v>
+        <v>62.89780050171086</v>
       </c>
       <c r="O40" t="n">
-        <v>78.55850566495744</v>
+        <v>78.61457070130248</v>
       </c>
       <c r="P40" t="n">
-        <v>86.47488929504921</v>
+        <v>86.52286261917671</v>
       </c>
       <c r="Q40" t="n">
         <v>65.34295837775146</v>
@@ -11037,28 +11037,28 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>100.8636683457816</v>
+        <v>100.9387195582597</v>
       </c>
       <c r="K41" t="n">
-        <v>99.91746411030702</v>
+        <v>100.0299464227919</v>
       </c>
       <c r="L41" t="n">
-        <v>86.68194260817799</v>
+        <v>86.82148686318189</v>
       </c>
       <c r="M41" t="n">
-        <v>64.46103222224738</v>
+        <v>64.61630209323866</v>
       </c>
       <c r="N41" t="n">
-        <v>60.84366661166607</v>
+        <v>61.00144891149961</v>
       </c>
       <c r="O41" t="n">
-        <v>70.92290991414882</v>
+        <v>71.07189926570237</v>
       </c>
       <c r="P41" t="n">
-        <v>95.38055856933971</v>
+        <v>95.50771753390021</v>
       </c>
       <c r="Q41" t="n">
-        <v>120.286167261384</v>
+        <v>120.3816583481039</v>
       </c>
       <c r="R41" t="n">
         <v>65.71641987298243</v>
@@ -11116,28 +11116,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J42" t="n">
-        <v>79.08163610062888</v>
+        <v>79.12633608862856</v>
       </c>
       <c r="K42" t="n">
-        <v>56.21884463473624</v>
+        <v>56.29524403393702</v>
       </c>
       <c r="L42" t="n">
-        <v>28.8027288364778</v>
+        <v>28.90545725697471</v>
       </c>
       <c r="M42" t="n">
-        <v>14.05903392201816</v>
+        <v>14.17891314335149</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>22.33166897274617</v>
+        <v>22.44423757443683</v>
       </c>
       <c r="P42" t="n">
-        <v>37.45148288602822</v>
+        <v>37.54182911310821</v>
       </c>
       <c r="Q42" t="n">
-        <v>75.4587552180969</v>
+        <v>75.5191492782957</v>
       </c>
       <c r="R42" t="n">
         <v>45.52166981132082</v>
@@ -11198,22 +11198,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K43" t="n">
-        <v>79.77883194102714</v>
+        <v>79.82491575659759</v>
       </c>
       <c r="L43" t="n">
-        <v>71.88156152713984</v>
+        <v>71.94053294496764</v>
       </c>
       <c r="M43" t="n">
-        <v>72.49783312793285</v>
+        <v>72.56001021962936</v>
       </c>
       <c r="N43" t="n">
-        <v>62.83710184228225</v>
+        <v>62.89780050171086</v>
       </c>
       <c r="O43" t="n">
-        <v>78.55850566495744</v>
+        <v>78.61457070130248</v>
       </c>
       <c r="P43" t="n">
-        <v>86.47488929504922</v>
+        <v>86.52286261917671</v>
       </c>
       <c r="Q43" t="n">
         <v>65.34295837775146</v>
@@ -11274,28 +11274,28 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>100.8636683457816</v>
+        <v>100.9387195582597</v>
       </c>
       <c r="K44" t="n">
-        <v>99.91746411030702</v>
+        <v>100.0299464227919</v>
       </c>
       <c r="L44" t="n">
-        <v>86.68194260817799</v>
+        <v>86.82148686318189</v>
       </c>
       <c r="M44" t="n">
-        <v>64.46103222224738</v>
+        <v>64.61630209323866</v>
       </c>
       <c r="N44" t="n">
-        <v>60.84366661166607</v>
+        <v>61.00144891149961</v>
       </c>
       <c r="O44" t="n">
-        <v>70.92290991414882</v>
+        <v>71.07189926570237</v>
       </c>
       <c r="P44" t="n">
-        <v>95.38055856933971</v>
+        <v>95.50771753390021</v>
       </c>
       <c r="Q44" t="n">
-        <v>120.286167261384</v>
+        <v>120.3816583481039</v>
       </c>
       <c r="R44" t="n">
         <v>65.71641987298243</v>
@@ -11353,28 +11353,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J45" t="n">
-        <v>79.08163610062888</v>
+        <v>79.12633608862856</v>
       </c>
       <c r="K45" t="n">
-        <v>56.21884463473624</v>
+        <v>56.29524403393702</v>
       </c>
       <c r="L45" t="n">
-        <v>28.8027288364778</v>
+        <v>28.90545725697471</v>
       </c>
       <c r="M45" t="n">
-        <v>14.05903392201816</v>
+        <v>14.17891314335149</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>22.33166897274616</v>
+        <v>22.44423757443683</v>
       </c>
       <c r="P45" t="n">
-        <v>37.45148288602822</v>
+        <v>37.54182911310821</v>
       </c>
       <c r="Q45" t="n">
-        <v>75.4587552180969</v>
+        <v>75.5191492782957</v>
       </c>
       <c r="R45" t="n">
         <v>45.52166981132082</v>
@@ -11435,22 +11435,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K46" t="n">
-        <v>79.77883194102714</v>
+        <v>79.82491575659759</v>
       </c>
       <c r="L46" t="n">
-        <v>71.88156152713984</v>
+        <v>71.94053294496764</v>
       </c>
       <c r="M46" t="n">
-        <v>72.49783312793285</v>
+        <v>72.56001021962936</v>
       </c>
       <c r="N46" t="n">
-        <v>62.83710184228225</v>
+        <v>62.89780050171086</v>
       </c>
       <c r="O46" t="n">
-        <v>78.55850566495744</v>
+        <v>78.61457070130248</v>
       </c>
       <c r="P46" t="n">
-        <v>86.47488929504921</v>
+        <v>86.52286261917671</v>
       </c>
       <c r="Q46" t="n">
         <v>65.34295837775146</v>
@@ -23230,13 +23230,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G11" t="n">
-        <v>414.3580138970446</v>
+        <v>414.3588981658848</v>
       </c>
       <c r="H11" t="n">
-        <v>329.7996513619983</v>
+        <v>329.8087073802583</v>
       </c>
       <c r="I11" t="n">
-        <v>174.0544322839737</v>
+        <v>174.0885230584365</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -23263,16 +23263,16 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>90.52512296627523</v>
+        <v>90.58066941881005</v>
       </c>
       <c r="S11" t="n">
-        <v>187.4921801390091</v>
+        <v>187.5123304152058</v>
       </c>
       <c r="T11" t="n">
-        <v>218.9603219259404</v>
+        <v>218.9641928127885</v>
       </c>
       <c r="U11" t="n">
-        <v>251.2700750183893</v>
+        <v>251.2701457598965</v>
       </c>
       <c r="V11" t="n">
         <v>327.7522584701349</v>
@@ -23309,13 +23309,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G12" t="n">
-        <v>136.8380454650974</v>
+        <v>136.8385185906377</v>
       </c>
       <c r="H12" t="n">
-        <v>107.3536517836663</v>
+        <v>107.3582211803319</v>
       </c>
       <c r="I12" t="n">
-        <v>71.9933309646226</v>
+        <v>72.00962059397116</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -23342,16 +23342,16 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>68.77424924698271</v>
+        <v>68.80362453272261</v>
       </c>
       <c r="S12" t="n">
-        <v>162.2942560094982</v>
+        <v>162.3030441088983</v>
       </c>
       <c r="T12" t="n">
-        <v>198.1273230344442</v>
+        <v>198.1292300623896</v>
       </c>
       <c r="U12" t="n">
-        <v>225.9081273639937</v>
+        <v>225.908158490674</v>
       </c>
       <c r="V12" t="n">
         <v>232.8005871494253</v>
@@ -23388,16 +23388,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G13" t="n">
-        <v>167.5672088666555</v>
+        <v>167.5676055192152</v>
       </c>
       <c r="H13" t="n">
-        <v>158.4594675894068</v>
+        <v>158.4629941912556</v>
       </c>
       <c r="I13" t="n">
-        <v>142.7065405010288</v>
+        <v>142.7184689252781</v>
       </c>
       <c r="J13" t="n">
-        <v>63.39860634618094</v>
+        <v>63.42664968215054</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -23418,19 +23418,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>50.67704325169434</v>
+        <v>50.71025749466926</v>
       </c>
       <c r="R13" t="n">
-        <v>158.2391290820875</v>
+        <v>158.2569640235438</v>
       </c>
       <c r="S13" t="n">
-        <v>216.631434102546</v>
+        <v>216.6383466748816</v>
       </c>
       <c r="T13" t="n">
-        <v>226.1349336905766</v>
+        <v>226.1366284787861</v>
       </c>
       <c r="U13" t="n">
-        <v>286.2959146023925</v>
+        <v>286.2959362379867</v>
       </c>
       <c r="V13" t="n">
         <v>252.137643323828</v>
@@ -23467,13 +23467,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G14" t="n">
-        <v>414.3580138970446</v>
+        <v>414.3588981658848</v>
       </c>
       <c r="H14" t="n">
-        <v>329.7996513619983</v>
+        <v>329.8087073802583</v>
       </c>
       <c r="I14" t="n">
-        <v>174.0544322839737</v>
+        <v>174.0885230584365</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -23500,16 +23500,16 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>90.52512296627523</v>
+        <v>90.58066941881005</v>
       </c>
       <c r="S14" t="n">
-        <v>187.4921801390091</v>
+        <v>187.5123304152058</v>
       </c>
       <c r="T14" t="n">
-        <v>218.9603219259404</v>
+        <v>218.9641928127885</v>
       </c>
       <c r="U14" t="n">
-        <v>251.2700750183893</v>
+        <v>251.2701457598965</v>
       </c>
       <c r="V14" t="n">
         <v>327.7522584701349</v>
@@ -23546,13 +23546,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G15" t="n">
-        <v>136.8380454650974</v>
+        <v>136.8385185906377</v>
       </c>
       <c r="H15" t="n">
-        <v>107.3536517836663</v>
+        <v>107.3582211803319</v>
       </c>
       <c r="I15" t="n">
-        <v>71.9933309646226</v>
+        <v>72.00962059397116</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -23579,16 +23579,16 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>68.77424924698271</v>
+        <v>68.80362453272261</v>
       </c>
       <c r="S15" t="n">
-        <v>162.2942560094982</v>
+        <v>162.3030441088983</v>
       </c>
       <c r="T15" t="n">
-        <v>198.1273230344442</v>
+        <v>198.1292300623896</v>
       </c>
       <c r="U15" t="n">
-        <v>225.9081273639937</v>
+        <v>225.908158490674</v>
       </c>
       <c r="V15" t="n">
         <v>232.8005871494253</v>
@@ -23625,16 +23625,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G16" t="n">
-        <v>167.5672088666555</v>
+        <v>167.5676055192152</v>
       </c>
       <c r="H16" t="n">
-        <v>158.4594675894068</v>
+        <v>158.4629941912556</v>
       </c>
       <c r="I16" t="n">
-        <v>142.7065405010288</v>
+        <v>142.7184689252781</v>
       </c>
       <c r="J16" t="n">
-        <v>63.39860634618094</v>
+        <v>63.42664968215054</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -23655,19 +23655,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>50.67704325169434</v>
+        <v>50.71025749466926</v>
       </c>
       <c r="R16" t="n">
-        <v>158.2391290820875</v>
+        <v>158.2569640235438</v>
       </c>
       <c r="S16" t="n">
-        <v>216.631434102546</v>
+        <v>216.6383466748816</v>
       </c>
       <c r="T16" t="n">
-        <v>226.1349336905766</v>
+        <v>226.1366284787861</v>
       </c>
       <c r="U16" t="n">
-        <v>286.2959146023925</v>
+        <v>286.2959362379867</v>
       </c>
       <c r="V16" t="n">
         <v>252.137643323828</v>
@@ -23704,13 +23704,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G17" t="n">
-        <v>414.3580138970446</v>
+        <v>414.3588981658848</v>
       </c>
       <c r="H17" t="n">
-        <v>329.7996513619983</v>
+        <v>329.8087073802583</v>
       </c>
       <c r="I17" t="n">
-        <v>174.0544322839737</v>
+        <v>174.0885230584365</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -23737,16 +23737,16 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>90.52512296627523</v>
+        <v>90.58066941881005</v>
       </c>
       <c r="S17" t="n">
-        <v>187.4921801390091</v>
+        <v>187.5123304152058</v>
       </c>
       <c r="T17" t="n">
-        <v>218.9603219259404</v>
+        <v>218.9641928127885</v>
       </c>
       <c r="U17" t="n">
-        <v>251.2700750183893</v>
+        <v>251.2701457598965</v>
       </c>
       <c r="V17" t="n">
         <v>327.7522584701349</v>
@@ -23783,13 +23783,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G18" t="n">
-        <v>136.8380454650974</v>
+        <v>136.8385185906377</v>
       </c>
       <c r="H18" t="n">
-        <v>107.3536517836663</v>
+        <v>107.3582211803319</v>
       </c>
       <c r="I18" t="n">
-        <v>71.9933309646226</v>
+        <v>72.00962059397116</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -23816,16 +23816,16 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>68.77424924698271</v>
+        <v>68.80362453272261</v>
       </c>
       <c r="S18" t="n">
-        <v>162.2942560094982</v>
+        <v>162.3030441088983</v>
       </c>
       <c r="T18" t="n">
-        <v>198.1273230344442</v>
+        <v>198.1292300623896</v>
       </c>
       <c r="U18" t="n">
-        <v>225.9081273639937</v>
+        <v>225.908158490674</v>
       </c>
       <c r="V18" t="n">
         <v>232.8005871494253</v>
@@ -23862,16 +23862,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G19" t="n">
-        <v>167.5672088666555</v>
+        <v>167.5676055192152</v>
       </c>
       <c r="H19" t="n">
-        <v>158.4594675894068</v>
+        <v>158.4629941912556</v>
       </c>
       <c r="I19" t="n">
-        <v>142.7065405010288</v>
+        <v>142.7184689252781</v>
       </c>
       <c r="J19" t="n">
-        <v>63.39860634618094</v>
+        <v>63.42664968215054</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -23892,19 +23892,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>50.67704325169434</v>
+        <v>50.71025749466926</v>
       </c>
       <c r="R19" t="n">
-        <v>158.2391290820875</v>
+        <v>158.2569640235438</v>
       </c>
       <c r="S19" t="n">
-        <v>216.631434102546</v>
+        <v>216.6383466748816</v>
       </c>
       <c r="T19" t="n">
-        <v>226.1349336905766</v>
+        <v>226.1366284787861</v>
       </c>
       <c r="U19" t="n">
-        <v>286.2959146023925</v>
+        <v>286.2959362379867</v>
       </c>
       <c r="V19" t="n">
         <v>252.137643323828</v>
@@ -23941,13 +23941,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G20" t="n">
-        <v>414.3580138970446</v>
+        <v>414.3588981658848</v>
       </c>
       <c r="H20" t="n">
-        <v>329.7996513619983</v>
+        <v>329.8087073802583</v>
       </c>
       <c r="I20" t="n">
-        <v>174.0544322839737</v>
+        <v>174.0885230584365</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -23974,16 +23974,16 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>90.52512296627523</v>
+        <v>90.58066941881005</v>
       </c>
       <c r="S20" t="n">
-        <v>187.4921801390091</v>
+        <v>187.5123304152058</v>
       </c>
       <c r="T20" t="n">
-        <v>218.9603219259404</v>
+        <v>218.9641928127885</v>
       </c>
       <c r="U20" t="n">
-        <v>251.2700750183893</v>
+        <v>251.2701457598965</v>
       </c>
       <c r="V20" t="n">
         <v>327.7522584701349</v>
@@ -24020,13 +24020,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G21" t="n">
-        <v>136.8380454650974</v>
+        <v>136.8385185906377</v>
       </c>
       <c r="H21" t="n">
-        <v>107.3536517836663</v>
+        <v>107.3582211803319</v>
       </c>
       <c r="I21" t="n">
-        <v>71.9933309646226</v>
+        <v>72.00962059397116</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -24053,16 +24053,16 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>68.77424924698271</v>
+        <v>68.80362453272261</v>
       </c>
       <c r="S21" t="n">
-        <v>162.2942560094982</v>
+        <v>162.3030441088983</v>
       </c>
       <c r="T21" t="n">
-        <v>198.1273230344442</v>
+        <v>198.1292300623896</v>
       </c>
       <c r="U21" t="n">
-        <v>225.9081273639937</v>
+        <v>225.908158490674</v>
       </c>
       <c r="V21" t="n">
         <v>232.8005871494253</v>
@@ -24099,16 +24099,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G22" t="n">
-        <v>167.5672088666555</v>
+        <v>167.5676055192152</v>
       </c>
       <c r="H22" t="n">
-        <v>158.4594675894068</v>
+        <v>158.4629941912556</v>
       </c>
       <c r="I22" t="n">
-        <v>142.7065405010288</v>
+        <v>142.7184689252781</v>
       </c>
       <c r="J22" t="n">
-        <v>63.39860634618094</v>
+        <v>63.42664968215054</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -24129,19 +24129,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>50.67704325169434</v>
+        <v>50.71025749466926</v>
       </c>
       <c r="R22" t="n">
-        <v>158.2391290820875</v>
+        <v>158.2569640235438</v>
       </c>
       <c r="S22" t="n">
-        <v>216.631434102546</v>
+        <v>216.6383466748816</v>
       </c>
       <c r="T22" t="n">
-        <v>226.1349336905766</v>
+        <v>226.1366284787861</v>
       </c>
       <c r="U22" t="n">
-        <v>286.2959146023925</v>
+        <v>286.2959362379867</v>
       </c>
       <c r="V22" t="n">
         <v>252.137643323828</v>
@@ -24178,13 +24178,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G23" t="n">
-        <v>414.3580138970446</v>
+        <v>414.3588981658848</v>
       </c>
       <c r="H23" t="n">
-        <v>329.7996513619983</v>
+        <v>329.8087073802583</v>
       </c>
       <c r="I23" t="n">
-        <v>174.0544322839737</v>
+        <v>174.0885230584365</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -24211,16 +24211,16 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>90.52512296627523</v>
+        <v>90.58066941881005</v>
       </c>
       <c r="S23" t="n">
-        <v>187.4921801390091</v>
+        <v>187.5123304152058</v>
       </c>
       <c r="T23" t="n">
-        <v>218.9603219259404</v>
+        <v>218.9641928127885</v>
       </c>
       <c r="U23" t="n">
-        <v>251.2700750183893</v>
+        <v>251.2701457598965</v>
       </c>
       <c r="V23" t="n">
         <v>327.7522584701349</v>
@@ -24257,13 +24257,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G24" t="n">
-        <v>136.8380454650974</v>
+        <v>136.8385185906377</v>
       </c>
       <c r="H24" t="n">
-        <v>107.3536517836663</v>
+        <v>107.3582211803319</v>
       </c>
       <c r="I24" t="n">
-        <v>71.9933309646226</v>
+        <v>72.00962059397116</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -24290,16 +24290,16 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>68.77424924698271</v>
+        <v>68.80362453272261</v>
       </c>
       <c r="S24" t="n">
-        <v>162.2942560094982</v>
+        <v>162.3030441088983</v>
       </c>
       <c r="T24" t="n">
-        <v>198.1273230344442</v>
+        <v>198.1292300623896</v>
       </c>
       <c r="U24" t="n">
-        <v>225.9081273639937</v>
+        <v>225.908158490674</v>
       </c>
       <c r="V24" t="n">
         <v>232.8005871494253</v>
@@ -24336,16 +24336,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G25" t="n">
-        <v>167.5672088666555</v>
+        <v>167.5676055192152</v>
       </c>
       <c r="H25" t="n">
-        <v>158.4594675894068</v>
+        <v>158.4629941912556</v>
       </c>
       <c r="I25" t="n">
-        <v>142.7065405010288</v>
+        <v>142.7184689252781</v>
       </c>
       <c r="J25" t="n">
-        <v>63.39860634618094</v>
+        <v>63.42664968215054</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -24366,19 +24366,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>50.67704325169434</v>
+        <v>50.71025749466926</v>
       </c>
       <c r="R25" t="n">
-        <v>158.2391290820875</v>
+        <v>158.2569640235438</v>
       </c>
       <c r="S25" t="n">
-        <v>216.631434102546</v>
+        <v>216.6383466748816</v>
       </c>
       <c r="T25" t="n">
-        <v>226.1349336905766</v>
+        <v>226.1366284787861</v>
       </c>
       <c r="U25" t="n">
-        <v>286.2959146023925</v>
+        <v>286.2959362379867</v>
       </c>
       <c r="V25" t="n">
         <v>252.137643323828</v>
@@ -24415,13 +24415,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G26" t="n">
-        <v>414.3580138970446</v>
+        <v>414.3588981658848</v>
       </c>
       <c r="H26" t="n">
-        <v>329.7996513619983</v>
+        <v>329.8087073802583</v>
       </c>
       <c r="I26" t="n">
-        <v>174.0544322839737</v>
+        <v>174.0885230584365</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -24448,16 +24448,16 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>90.52512296627523</v>
+        <v>90.58066941881005</v>
       </c>
       <c r="S26" t="n">
-        <v>187.4921801390091</v>
+        <v>187.5123304152058</v>
       </c>
       <c r="T26" t="n">
-        <v>218.9603219259404</v>
+        <v>218.9641928127885</v>
       </c>
       <c r="U26" t="n">
-        <v>251.2700750183893</v>
+        <v>251.2701457598965</v>
       </c>
       <c r="V26" t="n">
         <v>327.7522584701349</v>
@@ -24494,13 +24494,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G27" t="n">
-        <v>136.8380454650974</v>
+        <v>136.8385185906377</v>
       </c>
       <c r="H27" t="n">
-        <v>107.3536517836663</v>
+        <v>107.3582211803319</v>
       </c>
       <c r="I27" t="n">
-        <v>71.9933309646226</v>
+        <v>72.00962059397116</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -24527,16 +24527,16 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>68.77424924698271</v>
+        <v>68.80362453272261</v>
       </c>
       <c r="S27" t="n">
-        <v>162.2942560094982</v>
+        <v>162.3030441088983</v>
       </c>
       <c r="T27" t="n">
-        <v>198.1273230344442</v>
+        <v>198.1292300623896</v>
       </c>
       <c r="U27" t="n">
-        <v>225.9081273639937</v>
+        <v>225.908158490674</v>
       </c>
       <c r="V27" t="n">
         <v>232.8005871494253</v>
@@ -24573,16 +24573,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G28" t="n">
-        <v>167.5672088666555</v>
+        <v>167.5676055192152</v>
       </c>
       <c r="H28" t="n">
-        <v>158.4594675894068</v>
+        <v>158.4629941912556</v>
       </c>
       <c r="I28" t="n">
-        <v>142.7065405010288</v>
+        <v>142.7184689252781</v>
       </c>
       <c r="J28" t="n">
-        <v>63.39860634618094</v>
+        <v>63.42664968215054</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -24603,19 +24603,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>50.67704325169434</v>
+        <v>50.71025749466926</v>
       </c>
       <c r="R28" t="n">
-        <v>158.2391290820875</v>
+        <v>158.2569640235438</v>
       </c>
       <c r="S28" t="n">
-        <v>216.631434102546</v>
+        <v>216.6383466748816</v>
       </c>
       <c r="T28" t="n">
-        <v>226.1349336905766</v>
+        <v>226.1366284787861</v>
       </c>
       <c r="U28" t="n">
-        <v>286.2959146023925</v>
+        <v>286.2959362379867</v>
       </c>
       <c r="V28" t="n">
         <v>252.137643323828</v>
@@ -24652,13 +24652,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G29" t="n">
-        <v>414.3580138970446</v>
+        <v>414.3588981658848</v>
       </c>
       <c r="H29" t="n">
-        <v>329.7996513619983</v>
+        <v>329.8087073802583</v>
       </c>
       <c r="I29" t="n">
-        <v>174.0544322839737</v>
+        <v>174.0885230584365</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -24685,16 +24685,16 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>90.52512296627523</v>
+        <v>90.58066941881005</v>
       </c>
       <c r="S29" t="n">
-        <v>187.4921801390091</v>
+        <v>187.5123304152058</v>
       </c>
       <c r="T29" t="n">
-        <v>218.9603219259404</v>
+        <v>218.9641928127885</v>
       </c>
       <c r="U29" t="n">
-        <v>251.2700750183893</v>
+        <v>251.2701457598965</v>
       </c>
       <c r="V29" t="n">
         <v>327.7522584701349</v>
@@ -24731,13 +24731,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G30" t="n">
-        <v>136.8380454650974</v>
+        <v>136.8385185906377</v>
       </c>
       <c r="H30" t="n">
-        <v>107.3536517836663</v>
+        <v>107.3582211803319</v>
       </c>
       <c r="I30" t="n">
-        <v>71.9933309646226</v>
+        <v>72.00962059397116</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -24764,16 +24764,16 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>68.77424924698271</v>
+        <v>68.80362453272261</v>
       </c>
       <c r="S30" t="n">
-        <v>162.2942560094982</v>
+        <v>162.3030441088983</v>
       </c>
       <c r="T30" t="n">
-        <v>198.1273230344442</v>
+        <v>198.1292300623896</v>
       </c>
       <c r="U30" t="n">
-        <v>225.9081273639937</v>
+        <v>225.908158490674</v>
       </c>
       <c r="V30" t="n">
         <v>232.8005871494253</v>
@@ -24810,16 +24810,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G31" t="n">
-        <v>167.5672088666555</v>
+        <v>167.5676055192152</v>
       </c>
       <c r="H31" t="n">
-        <v>158.4594675894068</v>
+        <v>158.4629941912556</v>
       </c>
       <c r="I31" t="n">
-        <v>142.7065405010288</v>
+        <v>142.7184689252781</v>
       </c>
       <c r="J31" t="n">
-        <v>63.39860634618094</v>
+        <v>63.42664968215054</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -24840,19 +24840,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>50.67704325169434</v>
+        <v>50.71025749466926</v>
       </c>
       <c r="R31" t="n">
-        <v>158.2391290820875</v>
+        <v>158.2569640235438</v>
       </c>
       <c r="S31" t="n">
-        <v>216.631434102546</v>
+        <v>216.6383466748816</v>
       </c>
       <c r="T31" t="n">
-        <v>226.1349336905766</v>
+        <v>226.1366284787861</v>
       </c>
       <c r="U31" t="n">
-        <v>286.2959146023925</v>
+        <v>286.2959362379867</v>
       </c>
       <c r="V31" t="n">
         <v>252.137643323828</v>
@@ -24889,13 +24889,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G32" t="n">
-        <v>414.3580138970446</v>
+        <v>414.3588981658848</v>
       </c>
       <c r="H32" t="n">
-        <v>329.7996513619983</v>
+        <v>329.8087073802583</v>
       </c>
       <c r="I32" t="n">
-        <v>174.0544322839737</v>
+        <v>174.0885230584365</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -24922,16 +24922,16 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>90.52512296627523</v>
+        <v>90.58066941881005</v>
       </c>
       <c r="S32" t="n">
-        <v>187.4921801390091</v>
+        <v>187.5123304152058</v>
       </c>
       <c r="T32" t="n">
-        <v>218.9603219259404</v>
+        <v>218.9641928127885</v>
       </c>
       <c r="U32" t="n">
-        <v>251.2700750183893</v>
+        <v>251.2701457598965</v>
       </c>
       <c r="V32" t="n">
         <v>327.7522584701349</v>
@@ -24968,13 +24968,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G33" t="n">
-        <v>136.8380454650974</v>
+        <v>136.8385185906377</v>
       </c>
       <c r="H33" t="n">
-        <v>107.3536517836663</v>
+        <v>107.3582211803319</v>
       </c>
       <c r="I33" t="n">
-        <v>71.9933309646226</v>
+        <v>72.00962059397116</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -25001,16 +25001,16 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>68.77424924698271</v>
+        <v>68.80362453272261</v>
       </c>
       <c r="S33" t="n">
-        <v>162.2942560094982</v>
+        <v>162.3030441088983</v>
       </c>
       <c r="T33" t="n">
-        <v>198.1273230344442</v>
+        <v>198.1292300623896</v>
       </c>
       <c r="U33" t="n">
-        <v>225.9081273639937</v>
+        <v>225.908158490674</v>
       </c>
       <c r="V33" t="n">
         <v>232.8005871494253</v>
@@ -25047,16 +25047,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G34" t="n">
-        <v>167.5672088666555</v>
+        <v>167.5676055192152</v>
       </c>
       <c r="H34" t="n">
-        <v>158.4594675894068</v>
+        <v>158.4629941912556</v>
       </c>
       <c r="I34" t="n">
-        <v>142.7065405010288</v>
+        <v>142.7184689252781</v>
       </c>
       <c r="J34" t="n">
-        <v>63.39860634618094</v>
+        <v>63.42664968215054</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -25077,19 +25077,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>50.67704325169434</v>
+        <v>50.71025749466926</v>
       </c>
       <c r="R34" t="n">
-        <v>158.2391290820875</v>
+        <v>158.2569640235438</v>
       </c>
       <c r="S34" t="n">
-        <v>216.631434102546</v>
+        <v>216.6383466748816</v>
       </c>
       <c r="T34" t="n">
-        <v>226.1349336905766</v>
+        <v>226.1366284787861</v>
       </c>
       <c r="U34" t="n">
-        <v>286.2959146023925</v>
+        <v>286.2959362379867</v>
       </c>
       <c r="V34" t="n">
         <v>252.137643323828</v>
@@ -25126,13 +25126,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G35" t="n">
-        <v>414.3580138970446</v>
+        <v>414.3588981658848</v>
       </c>
       <c r="H35" t="n">
-        <v>329.7996513619983</v>
+        <v>329.8087073802583</v>
       </c>
       <c r="I35" t="n">
-        <v>174.0544322839737</v>
+        <v>174.0885230584365</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -25159,16 +25159,16 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>90.52512296627523</v>
+        <v>90.58066941881005</v>
       </c>
       <c r="S35" t="n">
-        <v>187.4921801390091</v>
+        <v>187.5123304152058</v>
       </c>
       <c r="T35" t="n">
-        <v>218.9603219259404</v>
+        <v>218.9641928127885</v>
       </c>
       <c r="U35" t="n">
-        <v>251.2700750183893</v>
+        <v>251.2701457598965</v>
       </c>
       <c r="V35" t="n">
         <v>327.7522584701349</v>
@@ -25205,13 +25205,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G36" t="n">
-        <v>136.8380454650974</v>
+        <v>136.8385185906377</v>
       </c>
       <c r="H36" t="n">
-        <v>107.3536517836663</v>
+        <v>107.3582211803319</v>
       </c>
       <c r="I36" t="n">
-        <v>71.9933309646226</v>
+        <v>72.00962059397116</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -25238,16 +25238,16 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>68.77424924698271</v>
+        <v>68.80362453272261</v>
       </c>
       <c r="S36" t="n">
-        <v>162.2942560094982</v>
+        <v>162.3030441088983</v>
       </c>
       <c r="T36" t="n">
-        <v>198.1273230344442</v>
+        <v>198.1292300623896</v>
       </c>
       <c r="U36" t="n">
-        <v>225.9081273639937</v>
+        <v>225.908158490674</v>
       </c>
       <c r="V36" t="n">
         <v>232.8005871494253</v>
@@ -25284,16 +25284,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G37" t="n">
-        <v>167.5672088666555</v>
+        <v>167.5676055192152</v>
       </c>
       <c r="H37" t="n">
-        <v>158.4594675894068</v>
+        <v>158.4629941912556</v>
       </c>
       <c r="I37" t="n">
-        <v>142.7065405010288</v>
+        <v>142.7184689252781</v>
       </c>
       <c r="J37" t="n">
-        <v>63.39860634618094</v>
+        <v>63.42664968215054</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -25314,19 +25314,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>50.67704325169434</v>
+        <v>50.71025749466926</v>
       </c>
       <c r="R37" t="n">
-        <v>158.2391290820875</v>
+        <v>158.2569640235438</v>
       </c>
       <c r="S37" t="n">
-        <v>216.631434102546</v>
+        <v>216.6383466748816</v>
       </c>
       <c r="T37" t="n">
-        <v>226.1349336905766</v>
+        <v>226.1366284787861</v>
       </c>
       <c r="U37" t="n">
-        <v>286.2959146023925</v>
+        <v>286.2959362379867</v>
       </c>
       <c r="V37" t="n">
         <v>252.137643323828</v>
@@ -25363,13 +25363,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G38" t="n">
-        <v>414.3580138970446</v>
+        <v>414.3588981658848</v>
       </c>
       <c r="H38" t="n">
-        <v>329.7996513619983</v>
+        <v>329.8087073802583</v>
       </c>
       <c r="I38" t="n">
-        <v>174.0544322839737</v>
+        <v>174.0885230584365</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -25396,16 +25396,16 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>90.52512296627523</v>
+        <v>90.58066941881005</v>
       </c>
       <c r="S38" t="n">
-        <v>187.4921801390091</v>
+        <v>187.5123304152058</v>
       </c>
       <c r="T38" t="n">
-        <v>218.9603219259404</v>
+        <v>218.9641928127885</v>
       </c>
       <c r="U38" t="n">
-        <v>251.2700750183893</v>
+        <v>251.2701457598965</v>
       </c>
       <c r="V38" t="n">
         <v>327.7522584701349</v>
@@ -25442,13 +25442,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G39" t="n">
-        <v>136.8380454650974</v>
+        <v>136.8385185906377</v>
       </c>
       <c r="H39" t="n">
-        <v>107.3536517836663</v>
+        <v>107.3582211803319</v>
       </c>
       <c r="I39" t="n">
-        <v>71.9933309646226</v>
+        <v>72.00962059397116</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -25475,16 +25475,16 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>68.77424924698271</v>
+        <v>68.80362453272261</v>
       </c>
       <c r="S39" t="n">
-        <v>162.2942560094982</v>
+        <v>162.3030441088983</v>
       </c>
       <c r="T39" t="n">
-        <v>198.1273230344442</v>
+        <v>198.1292300623896</v>
       </c>
       <c r="U39" t="n">
-        <v>225.9081273639937</v>
+        <v>225.908158490674</v>
       </c>
       <c r="V39" t="n">
         <v>232.8005871494253</v>
@@ -25521,16 +25521,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G40" t="n">
-        <v>167.5672088666555</v>
+        <v>167.5676055192152</v>
       </c>
       <c r="H40" t="n">
-        <v>158.4594675894068</v>
+        <v>158.4629941912556</v>
       </c>
       <c r="I40" t="n">
-        <v>142.7065405010288</v>
+        <v>142.7184689252781</v>
       </c>
       <c r="J40" t="n">
-        <v>63.39860634618094</v>
+        <v>63.42664968215054</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -25551,19 +25551,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>50.67704325169434</v>
+        <v>50.71025749466926</v>
       </c>
       <c r="R40" t="n">
-        <v>158.2391290820875</v>
+        <v>158.2569640235438</v>
       </c>
       <c r="S40" t="n">
-        <v>216.631434102546</v>
+        <v>216.6383466748816</v>
       </c>
       <c r="T40" t="n">
-        <v>226.1349336905766</v>
+        <v>226.1366284787861</v>
       </c>
       <c r="U40" t="n">
-        <v>286.2959146023925</v>
+        <v>286.2959362379867</v>
       </c>
       <c r="V40" t="n">
         <v>252.137643323828</v>
@@ -25600,13 +25600,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G41" t="n">
-        <v>414.3580138970446</v>
+        <v>414.3588981658848</v>
       </c>
       <c r="H41" t="n">
-        <v>329.7996513619983</v>
+        <v>329.8087073802583</v>
       </c>
       <c r="I41" t="n">
-        <v>174.0544322839737</v>
+        <v>174.0885230584365</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -25633,16 +25633,16 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>90.52512296627522</v>
+        <v>90.58066941881005</v>
       </c>
       <c r="S41" t="n">
-        <v>187.4921801390091</v>
+        <v>187.5123304152058</v>
       </c>
       <c r="T41" t="n">
-        <v>218.9603219259404</v>
+        <v>218.9641928127885</v>
       </c>
       <c r="U41" t="n">
-        <v>251.2700750183893</v>
+        <v>251.2701457598965</v>
       </c>
       <c r="V41" t="n">
         <v>327.7522584701349</v>
@@ -25679,13 +25679,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G42" t="n">
-        <v>136.8380454650974</v>
+        <v>136.8385185906377</v>
       </c>
       <c r="H42" t="n">
-        <v>107.3536517836663</v>
+        <v>107.3582211803319</v>
       </c>
       <c r="I42" t="n">
-        <v>71.9933309646226</v>
+        <v>72.00962059397116</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -25712,16 +25712,16 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>68.77424924698271</v>
+        <v>68.80362453272261</v>
       </c>
       <c r="S42" t="n">
-        <v>162.2942560094982</v>
+        <v>162.3030441088983</v>
       </c>
       <c r="T42" t="n">
-        <v>198.1273230344442</v>
+        <v>198.1292300623896</v>
       </c>
       <c r="U42" t="n">
-        <v>225.9081273639937</v>
+        <v>225.908158490674</v>
       </c>
       <c r="V42" t="n">
         <v>232.8005871494253</v>
@@ -25758,16 +25758,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G43" t="n">
-        <v>167.5672088666555</v>
+        <v>167.5676055192152</v>
       </c>
       <c r="H43" t="n">
-        <v>158.4594675894068</v>
+        <v>158.4629941912556</v>
       </c>
       <c r="I43" t="n">
-        <v>142.7065405010288</v>
+        <v>142.7184689252781</v>
       </c>
       <c r="J43" t="n">
-        <v>63.39860634618093</v>
+        <v>63.42664968215054</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -25788,19 +25788,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>50.67704325169434</v>
+        <v>50.71025749466926</v>
       </c>
       <c r="R43" t="n">
-        <v>158.2391290820875</v>
+        <v>158.2569640235438</v>
       </c>
       <c r="S43" t="n">
-        <v>216.631434102546</v>
+        <v>216.6383466748816</v>
       </c>
       <c r="T43" t="n">
-        <v>226.1349336905766</v>
+        <v>226.1366284787861</v>
       </c>
       <c r="U43" t="n">
-        <v>286.2959146023925</v>
+        <v>286.2959362379867</v>
       </c>
       <c r="V43" t="n">
         <v>252.137643323828</v>
@@ -25837,13 +25837,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G44" t="n">
-        <v>414.3580138970446</v>
+        <v>414.3588981658848</v>
       </c>
       <c r="H44" t="n">
-        <v>329.7996513619983</v>
+        <v>329.8087073802583</v>
       </c>
       <c r="I44" t="n">
-        <v>174.0544322839737</v>
+        <v>174.0885230584365</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -25870,16 +25870,16 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>90.52512296627523</v>
+        <v>90.58066941881005</v>
       </c>
       <c r="S44" t="n">
-        <v>187.4921801390091</v>
+        <v>187.5123304152058</v>
       </c>
       <c r="T44" t="n">
-        <v>218.9603219259404</v>
+        <v>218.9641928127885</v>
       </c>
       <c r="U44" t="n">
-        <v>251.2700750183893</v>
+        <v>251.2701457598965</v>
       </c>
       <c r="V44" t="n">
         <v>327.7522584701349</v>
@@ -25916,13 +25916,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G45" t="n">
-        <v>136.8380454650974</v>
+        <v>136.8385185906377</v>
       </c>
       <c r="H45" t="n">
-        <v>107.3536517836663</v>
+        <v>107.3582211803319</v>
       </c>
       <c r="I45" t="n">
-        <v>71.9933309646226</v>
+        <v>72.00962059397116</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -25949,16 +25949,16 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>68.77424924698271</v>
+        <v>68.80362453272261</v>
       </c>
       <c r="S45" t="n">
-        <v>162.2942560094982</v>
+        <v>162.3030441088983</v>
       </c>
       <c r="T45" t="n">
-        <v>198.1273230344442</v>
+        <v>198.1292300623896</v>
       </c>
       <c r="U45" t="n">
-        <v>225.9081273639937</v>
+        <v>225.908158490674</v>
       </c>
       <c r="V45" t="n">
         <v>232.8005871494253</v>
@@ -25995,16 +25995,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G46" t="n">
-        <v>167.5672088666555</v>
+        <v>167.5676055192152</v>
       </c>
       <c r="H46" t="n">
-        <v>158.4594675894068</v>
+        <v>158.4629941912556</v>
       </c>
       <c r="I46" t="n">
-        <v>142.7065405010288</v>
+        <v>142.7184689252781</v>
       </c>
       <c r="J46" t="n">
-        <v>63.39860634618094</v>
+        <v>63.42664968215054</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -26025,19 +26025,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>50.67704325169434</v>
+        <v>50.71025749466926</v>
       </c>
       <c r="R46" t="n">
-        <v>158.2391290820875</v>
+        <v>158.2569640235438</v>
       </c>
       <c r="S46" t="n">
-        <v>216.631434102546</v>
+        <v>216.6383466748816</v>
       </c>
       <c r="T46" t="n">
-        <v>226.1349336905766</v>
+        <v>226.1366284787861</v>
       </c>
       <c r="U46" t="n">
-        <v>286.2959146023925</v>
+        <v>286.2959362379867</v>
       </c>
       <c r="V46" t="n">
         <v>252.137643323828</v>
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>344642.0443578188</v>
+        <v>344643.9841904797</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>344642.0443578188</v>
+        <v>344643.9841904797</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>344642.0443578188</v>
+        <v>344643.9841904797</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>344642.0443578188</v>
+        <v>344643.9841904797</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>344642.0443578188</v>
+        <v>344643.9841904797</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>344642.0443578188</v>
+        <v>344643.9841904797</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>344642.0443578188</v>
+        <v>344643.9841904797</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>344642.0443578188</v>
+        <v>344643.9841904797</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>344642.0443578188</v>
+        <v>344643.9841904797</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>344642.0443578188</v>
+        <v>344643.9841904797</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>344642.0443578188</v>
+        <v>344643.9841904797</v>
       </c>
     </row>
     <row r="16">
@@ -26190,7 +26190,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>344642.0443578188</v>
+        <v>344643.9841904797</v>
       </c>
     </row>
   </sheetData>
@@ -26267,43 +26267,43 @@
         <v>75255.18387201249</v>
       </c>
       <c r="D2" t="n">
-        <v>75255.18387201249</v>
+        <v>75255.18387201248</v>
       </c>
       <c r="E2" t="n">
-        <v>81671.9184170973</v>
+        <v>81666.69129627486</v>
       </c>
       <c r="F2" t="n">
-        <v>81671.9184170973</v>
+        <v>81666.69129627486</v>
       </c>
       <c r="G2" t="n">
-        <v>81671.91841709729</v>
+        <v>81666.69129627486</v>
       </c>
       <c r="H2" t="n">
-        <v>81671.91841709729</v>
+        <v>81666.69129627486</v>
       </c>
       <c r="I2" t="n">
-        <v>81671.9184170973</v>
+        <v>81666.69129627486</v>
       </c>
       <c r="J2" t="n">
-        <v>81671.91841709727</v>
+        <v>81666.69129627486</v>
       </c>
       <c r="K2" t="n">
-        <v>81671.91841709729</v>
+        <v>81666.69129627488</v>
       </c>
       <c r="L2" t="n">
-        <v>81671.91841709726</v>
+        <v>81666.69129627486</v>
       </c>
       <c r="M2" t="n">
-        <v>81671.91841709729</v>
+        <v>81666.69129627486</v>
       </c>
       <c r="N2" t="n">
-        <v>81671.91841709727</v>
+        <v>81666.69129627486</v>
       </c>
       <c r="O2" t="n">
-        <v>81671.91841709729</v>
+        <v>81666.69129627486</v>
       </c>
       <c r="P2" t="n">
-        <v>81671.91841709727</v>
+        <v>81666.69129627486</v>
       </c>
     </row>
     <row r="3">
@@ -26322,7 +26322,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>188799.7050000002</v>
+        <v>188622.9869705381</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -26365,49 +26365,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>43002.96221257856</v>
+        <v>41731.10116290394</v>
       </c>
       <c r="C4" t="n">
-        <v>43002.96221257856</v>
+        <v>41731.10116290394</v>
       </c>
       <c r="D4" t="n">
-        <v>43002.96221257856</v>
+        <v>41731.10116290394</v>
       </c>
       <c r="E4" t="n">
-        <v>17954.37068942963</v>
+        <v>17445.5225022092</v>
       </c>
       <c r="F4" t="n">
-        <v>17954.37068942963</v>
+        <v>17445.5225022092</v>
       </c>
       <c r="G4" t="n">
-        <v>17954.37068942963</v>
+        <v>17445.5225022092</v>
       </c>
       <c r="H4" t="n">
-        <v>17954.37068942963</v>
+        <v>17445.5225022092</v>
       </c>
       <c r="I4" t="n">
-        <v>17954.37068942963</v>
+        <v>17445.5225022092</v>
       </c>
       <c r="J4" t="n">
-        <v>17954.37068942963</v>
+        <v>17445.5225022092</v>
       </c>
       <c r="K4" t="n">
-        <v>17954.37068942963</v>
+        <v>17445.5225022092</v>
       </c>
       <c r="L4" t="n">
-        <v>17954.37068942963</v>
+        <v>17445.5225022092</v>
       </c>
       <c r="M4" t="n">
-        <v>17954.37068942963</v>
+        <v>17445.5225022092</v>
       </c>
       <c r="N4" t="n">
-        <v>17954.37068942963</v>
+        <v>17445.5225022092</v>
       </c>
       <c r="O4" t="n">
-        <v>17954.37068942963</v>
+        <v>17445.5225022092</v>
       </c>
       <c r="P4" t="n">
-        <v>17954.37068942963</v>
+        <v>17445.5225022092</v>
       </c>
     </row>
     <row r="5">
@@ -26426,40 +26426,40 @@
         <v>33627.6</v>
       </c>
       <c r="E5" t="n">
-        <v>5123.000000000007</v>
+        <v>5118.204831146673</v>
       </c>
       <c r="F5" t="n">
-        <v>5123.000000000007</v>
+        <v>5118.204831146673</v>
       </c>
       <c r="G5" t="n">
-        <v>5123.000000000007</v>
+        <v>5118.204831146673</v>
       </c>
       <c r="H5" t="n">
-        <v>5123.000000000007</v>
+        <v>5118.204831146673</v>
       </c>
       <c r="I5" t="n">
-        <v>5123.000000000007</v>
+        <v>5118.204831146673</v>
       </c>
       <c r="J5" t="n">
-        <v>5123.000000000007</v>
+        <v>5118.204831146673</v>
       </c>
       <c r="K5" t="n">
-        <v>5123.000000000007</v>
+        <v>5118.204831146673</v>
       </c>
       <c r="L5" t="n">
-        <v>5123.000000000007</v>
+        <v>5118.204831146673</v>
       </c>
       <c r="M5" t="n">
-        <v>5123.000000000007</v>
+        <v>5118.204831146673</v>
       </c>
       <c r="N5" t="n">
-        <v>5123.000000000007</v>
+        <v>5118.204831146673</v>
       </c>
       <c r="O5" t="n">
-        <v>5123.000000000007</v>
+        <v>5118.204831146673</v>
       </c>
       <c r="P5" t="n">
-        <v>5123.000000000007</v>
+        <v>5118.204831146673</v>
       </c>
     </row>
     <row r="6">
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1375.378340566065</v>
+        <v>-103.5172908914465</v>
       </c>
       <c r="C6" t="n">
-        <v>-1375.378340566065</v>
+        <v>-103.5172908914465</v>
       </c>
       <c r="D6" t="n">
-        <v>-1375.378340566065</v>
+        <v>-103.517290891461</v>
       </c>
       <c r="E6" t="n">
-        <v>-130205.1572723326</v>
+        <v>-129520.0230076192</v>
       </c>
       <c r="F6" t="n">
-        <v>58594.54772766766</v>
+        <v>59102.96396291898</v>
       </c>
       <c r="G6" t="n">
-        <v>58594.54772766765</v>
+        <v>59102.96396291898</v>
       </c>
       <c r="H6" t="n">
-        <v>58594.54772766765</v>
+        <v>59102.96396291898</v>
       </c>
       <c r="I6" t="n">
-        <v>58594.54772766766</v>
+        <v>59102.96396291898</v>
       </c>
       <c r="J6" t="n">
-        <v>58594.54772766763</v>
+        <v>59102.96396291898</v>
       </c>
       <c r="K6" t="n">
-        <v>58594.54772766765</v>
+        <v>59102.963962919</v>
       </c>
       <c r="L6" t="n">
-        <v>58594.54772766762</v>
+        <v>59102.96396291898</v>
       </c>
       <c r="M6" t="n">
-        <v>58594.54772766765</v>
+        <v>59102.96396291898</v>
       </c>
       <c r="N6" t="n">
-        <v>58594.54772766763</v>
+        <v>59102.96396291898</v>
       </c>
       <c r="O6" t="n">
-        <v>58594.54772766765</v>
+        <v>59102.96396291898</v>
       </c>
       <c r="P6" t="n">
-        <v>58594.54772766763</v>
+        <v>59102.96396291898</v>
       </c>
     </row>
   </sheetData>
@@ -26684,40 +26684,40 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>235.0000000000003</v>
+        <v>234.7800381259942</v>
       </c>
       <c r="F3" t="n">
-        <v>235.0000000000003</v>
+        <v>234.7800381259942</v>
       </c>
       <c r="G3" t="n">
-        <v>235.0000000000003</v>
+        <v>234.7800381259942</v>
       </c>
       <c r="H3" t="n">
-        <v>235.0000000000003</v>
+        <v>234.7800381259942</v>
       </c>
       <c r="I3" t="n">
-        <v>235.0000000000003</v>
+        <v>234.7800381259942</v>
       </c>
       <c r="J3" t="n">
-        <v>235.0000000000003</v>
+        <v>234.7800381259942</v>
       </c>
       <c r="K3" t="n">
-        <v>235.0000000000003</v>
+        <v>234.7800381259942</v>
       </c>
       <c r="L3" t="n">
-        <v>235.0000000000003</v>
+        <v>234.7800381259942</v>
       </c>
       <c r="M3" t="n">
-        <v>235.0000000000003</v>
+        <v>234.7800381259942</v>
       </c>
       <c r="N3" t="n">
-        <v>235.0000000000003</v>
+        <v>234.7800381259942</v>
       </c>
       <c r="O3" t="n">
-        <v>235.0000000000003</v>
+        <v>234.7800381259942</v>
       </c>
       <c r="P3" t="n">
-        <v>235.0000000000003</v>
+        <v>234.7800381259942</v>
       </c>
     </row>
     <row r="4">
@@ -26840,49 +26840,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -26898,43 +26898,43 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>235</v>
+        <v>234.7800381259942</v>
       </c>
       <c r="F3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -26944,7 +26944,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -26953,10 +26953,10 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -26968,25 +26968,25 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -31670,49 +31670,49 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9447236180904528</v>
+        <v>0.9438393492502272</v>
       </c>
       <c r="H11" t="n">
-        <v>9.675150753768852</v>
+        <v>9.666094735508892</v>
       </c>
       <c r="I11" t="n">
-        <v>36.42145728643222</v>
+        <v>36.38736651196942</v>
       </c>
       <c r="J11" t="n">
-        <v>80.18223618090464</v>
+        <v>80.10718496842655</v>
       </c>
       <c r="K11" t="n">
-        <v>120.1723869346735</v>
+        <v>120.0599046221887</v>
       </c>
       <c r="L11" t="n">
-        <v>149.0844723618092</v>
+        <v>148.9449281068053</v>
       </c>
       <c r="M11" t="n">
-        <v>165.8852010050254</v>
+        <v>165.7299311340341</v>
       </c>
       <c r="N11" t="n">
-        <v>168.5693969849249</v>
+        <v>168.4116146850913</v>
       </c>
       <c r="O11" t="n">
-        <v>159.1753015075379</v>
+        <v>159.0263121559844</v>
       </c>
       <c r="P11" t="n">
-        <v>135.8524371859298</v>
+        <v>135.7252782213693</v>
       </c>
       <c r="Q11" t="n">
-        <v>102.0195226130655</v>
+        <v>101.9240315263455</v>
       </c>
       <c r="R11" t="n">
-        <v>59.34399497487446</v>
+        <v>59.28844852233964</v>
       </c>
       <c r="S11" t="n">
-        <v>21.52788944723622</v>
+        <v>21.50773917103957</v>
       </c>
       <c r="T11" t="n">
-        <v>4.135527638190959</v>
+        <v>4.131656751342872</v>
       </c>
       <c r="U11" t="n">
-        <v>0.07557788944723622</v>
+        <v>0.07550714794001816</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -31749,49 +31749,49 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5054716981132082</v>
+        <v>0.5049985725728932</v>
       </c>
       <c r="H12" t="n">
-        <v>4.881792452830196</v>
+        <v>4.877223056164522</v>
       </c>
       <c r="I12" t="n">
-        <v>17.40330188679248</v>
+        <v>17.38701225744391</v>
       </c>
       <c r="J12" t="n">
-        <v>47.75599056603781</v>
+        <v>47.71129057803813</v>
       </c>
       <c r="K12" t="n">
-        <v>81.62259433962275</v>
+        <v>81.54619494042197</v>
       </c>
       <c r="L12" t="n">
-        <v>109.7516509433964</v>
+        <v>109.6489225228995</v>
       </c>
       <c r="M12" t="n">
-        <v>128.0750000000002</v>
+        <v>127.9551207786668</v>
       </c>
       <c r="N12" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O12" t="n">
-        <v>120.2645754716983</v>
+        <v>120.1520068700076</v>
       </c>
       <c r="P12" t="n">
-        <v>96.52292452830203</v>
+        <v>96.43257830122204</v>
       </c>
       <c r="Q12" t="n">
-        <v>64.52301886792462</v>
+        <v>64.46262480772582</v>
       </c>
       <c r="R12" t="n">
-        <v>31.38358490566043</v>
+        <v>31.35420961992052</v>
       </c>
       <c r="S12" t="n">
-        <v>9.388915094339628</v>
+        <v>9.380126994939479</v>
       </c>
       <c r="T12" t="n">
-        <v>2.03740566037736</v>
+        <v>2.035498632431968</v>
       </c>
       <c r="U12" t="n">
-        <v>0.03325471698113213</v>
+        <v>0.03322359030084825</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -31828,49 +31828,49 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4237704918032792</v>
+        <v>0.4233738392435961</v>
       </c>
       <c r="H13" t="n">
-        <v>3.767704918032794</v>
+        <v>3.764178316183975</v>
       </c>
       <c r="I13" t="n">
-        <v>12.74393442622953</v>
+        <v>12.73200600198015</v>
       </c>
       <c r="J13" t="n">
-        <v>29.96057377049184</v>
+        <v>29.93253043452224</v>
       </c>
       <c r="K13" t="n">
-        <v>49.23442622950824</v>
+        <v>49.18834241393778</v>
       </c>
       <c r="L13" t="n">
-        <v>63.00311475409845</v>
+        <v>62.94414333627064</v>
       </c>
       <c r="M13" t="n">
-        <v>66.4279508196722</v>
+        <v>66.36577372797569</v>
       </c>
       <c r="N13" t="n">
-        <v>64.84844262295094</v>
+        <v>64.78774396352233</v>
       </c>
       <c r="O13" t="n">
-        <v>59.89803278688535</v>
+        <v>59.84196775054031</v>
       </c>
       <c r="P13" t="n">
-        <v>51.25311475409841</v>
+        <v>51.20514142997091</v>
       </c>
       <c r="Q13" t="n">
-        <v>35.48500000000005</v>
+        <v>35.45178575702512</v>
       </c>
       <c r="R13" t="n">
-        <v>19.05426229508199</v>
+        <v>19.03642735362569</v>
       </c>
       <c r="S13" t="n">
-        <v>7.385163934426236</v>
+        <v>7.378251362090666</v>
       </c>
       <c r="T13" t="n">
-        <v>1.81065573770492</v>
+        <v>1.808960949495364</v>
       </c>
       <c r="U13" t="n">
-        <v>0.02311475409836071</v>
+        <v>0.02309311850419617</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -31907,49 +31907,49 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9447236180904528</v>
+        <v>0.9438393492502272</v>
       </c>
       <c r="H14" t="n">
-        <v>9.675150753768852</v>
+        <v>9.666094735508892</v>
       </c>
       <c r="I14" t="n">
-        <v>36.42145728643222</v>
+        <v>36.38736651196942</v>
       </c>
       <c r="J14" t="n">
-        <v>80.18223618090464</v>
+        <v>80.10718496842655</v>
       </c>
       <c r="K14" t="n">
-        <v>120.1723869346735</v>
+        <v>120.0599046221887</v>
       </c>
       <c r="L14" t="n">
-        <v>149.0844723618092</v>
+        <v>148.9449281068053</v>
       </c>
       <c r="M14" t="n">
-        <v>165.8852010050254</v>
+        <v>165.7299311340341</v>
       </c>
       <c r="N14" t="n">
-        <v>168.5693969849249</v>
+        <v>168.4116146850913</v>
       </c>
       <c r="O14" t="n">
-        <v>159.1753015075379</v>
+        <v>159.0263121559844</v>
       </c>
       <c r="P14" t="n">
-        <v>135.8524371859298</v>
+        <v>135.7252782213693</v>
       </c>
       <c r="Q14" t="n">
-        <v>102.0195226130655</v>
+        <v>101.9240315263455</v>
       </c>
       <c r="R14" t="n">
-        <v>59.34399497487446</v>
+        <v>59.28844852233964</v>
       </c>
       <c r="S14" t="n">
-        <v>21.52788944723622</v>
+        <v>21.50773917103957</v>
       </c>
       <c r="T14" t="n">
-        <v>4.135527638190959</v>
+        <v>4.131656751342872</v>
       </c>
       <c r="U14" t="n">
-        <v>0.07557788944723622</v>
+        <v>0.07550714794001816</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -31986,49 +31986,49 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5054716981132082</v>
+        <v>0.5049985725728932</v>
       </c>
       <c r="H15" t="n">
-        <v>4.881792452830196</v>
+        <v>4.877223056164522</v>
       </c>
       <c r="I15" t="n">
-        <v>17.40330188679248</v>
+        <v>17.38701225744391</v>
       </c>
       <c r="J15" t="n">
-        <v>47.75599056603781</v>
+        <v>47.71129057803813</v>
       </c>
       <c r="K15" t="n">
-        <v>81.62259433962275</v>
+        <v>81.54619494042197</v>
       </c>
       <c r="L15" t="n">
-        <v>109.7516509433964</v>
+        <v>109.6489225228995</v>
       </c>
       <c r="M15" t="n">
-        <v>128.0750000000002</v>
+        <v>127.9551207786668</v>
       </c>
       <c r="N15" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O15" t="n">
-        <v>120.2645754716983</v>
+        <v>120.1520068700076</v>
       </c>
       <c r="P15" t="n">
-        <v>96.52292452830203</v>
+        <v>96.43257830122204</v>
       </c>
       <c r="Q15" t="n">
-        <v>64.52301886792462</v>
+        <v>64.46262480772582</v>
       </c>
       <c r="R15" t="n">
-        <v>31.38358490566043</v>
+        <v>31.35420961992052</v>
       </c>
       <c r="S15" t="n">
-        <v>9.388915094339628</v>
+        <v>9.380126994939479</v>
       </c>
       <c r="T15" t="n">
-        <v>2.03740566037736</v>
+        <v>2.035498632431968</v>
       </c>
       <c r="U15" t="n">
-        <v>0.03325471698113213</v>
+        <v>0.03322359030084825</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -32065,49 +32065,49 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4237704918032792</v>
+        <v>0.4233738392435961</v>
       </c>
       <c r="H16" t="n">
-        <v>3.767704918032794</v>
+        <v>3.764178316183975</v>
       </c>
       <c r="I16" t="n">
-        <v>12.74393442622953</v>
+        <v>12.73200600198015</v>
       </c>
       <c r="J16" t="n">
-        <v>29.96057377049184</v>
+        <v>29.93253043452224</v>
       </c>
       <c r="K16" t="n">
-        <v>49.23442622950824</v>
+        <v>49.18834241393778</v>
       </c>
       <c r="L16" t="n">
-        <v>63.00311475409845</v>
+        <v>62.94414333627064</v>
       </c>
       <c r="M16" t="n">
-        <v>66.4279508196722</v>
+        <v>66.36577372797569</v>
       </c>
       <c r="N16" t="n">
-        <v>64.84844262295094</v>
+        <v>64.78774396352233</v>
       </c>
       <c r="O16" t="n">
-        <v>59.89803278688535</v>
+        <v>59.84196775054031</v>
       </c>
       <c r="P16" t="n">
-        <v>51.25311475409841</v>
+        <v>51.20514142997091</v>
       </c>
       <c r="Q16" t="n">
-        <v>35.48500000000005</v>
+        <v>35.45178575702512</v>
       </c>
       <c r="R16" t="n">
-        <v>19.05426229508199</v>
+        <v>19.03642735362569</v>
       </c>
       <c r="S16" t="n">
-        <v>7.385163934426236</v>
+        <v>7.378251362090666</v>
       </c>
       <c r="T16" t="n">
-        <v>1.81065573770492</v>
+        <v>1.808960949495364</v>
       </c>
       <c r="U16" t="n">
-        <v>0.02311475409836071</v>
+        <v>0.02309311850419617</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -32144,49 +32144,49 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9447236180904528</v>
+        <v>0.9438393492502272</v>
       </c>
       <c r="H17" t="n">
-        <v>9.675150753768852</v>
+        <v>9.666094735508892</v>
       </c>
       <c r="I17" t="n">
-        <v>36.42145728643222</v>
+        <v>36.38736651196942</v>
       </c>
       <c r="J17" t="n">
-        <v>80.18223618090464</v>
+        <v>80.10718496842655</v>
       </c>
       <c r="K17" t="n">
-        <v>120.1723869346735</v>
+        <v>120.0599046221887</v>
       </c>
       <c r="L17" t="n">
-        <v>149.0844723618092</v>
+        <v>148.9449281068053</v>
       </c>
       <c r="M17" t="n">
-        <v>165.8852010050254</v>
+        <v>165.7299311340341</v>
       </c>
       <c r="N17" t="n">
-        <v>168.5693969849249</v>
+        <v>168.4116146850913</v>
       </c>
       <c r="O17" t="n">
-        <v>159.1753015075379</v>
+        <v>159.0263121559844</v>
       </c>
       <c r="P17" t="n">
-        <v>135.8524371859298</v>
+        <v>135.7252782213693</v>
       </c>
       <c r="Q17" t="n">
-        <v>102.0195226130655</v>
+        <v>101.9240315263455</v>
       </c>
       <c r="R17" t="n">
-        <v>59.34399497487446</v>
+        <v>59.28844852233964</v>
       </c>
       <c r="S17" t="n">
-        <v>21.52788944723622</v>
+        <v>21.50773917103957</v>
       </c>
       <c r="T17" t="n">
-        <v>4.135527638190959</v>
+        <v>4.131656751342872</v>
       </c>
       <c r="U17" t="n">
-        <v>0.07557788944723622</v>
+        <v>0.07550714794001816</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -32223,49 +32223,49 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5054716981132082</v>
+        <v>0.5049985725728932</v>
       </c>
       <c r="H18" t="n">
-        <v>4.881792452830196</v>
+        <v>4.877223056164522</v>
       </c>
       <c r="I18" t="n">
-        <v>17.40330188679248</v>
+        <v>17.38701225744391</v>
       </c>
       <c r="J18" t="n">
-        <v>47.75599056603781</v>
+        <v>47.71129057803813</v>
       </c>
       <c r="K18" t="n">
-        <v>81.62259433962275</v>
+        <v>81.54619494042197</v>
       </c>
       <c r="L18" t="n">
-        <v>109.7516509433964</v>
+        <v>109.6489225228995</v>
       </c>
       <c r="M18" t="n">
-        <v>128.0750000000002</v>
+        <v>127.9551207786668</v>
       </c>
       <c r="N18" t="n">
-        <v>131.3417120833334</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O18" t="n">
-        <v>120.2645754716983</v>
+        <v>120.1520068700076</v>
       </c>
       <c r="P18" t="n">
-        <v>96.52292452830203</v>
+        <v>96.43257830122204</v>
       </c>
       <c r="Q18" t="n">
-        <v>64.52301886792462</v>
+        <v>64.46262480772582</v>
       </c>
       <c r="R18" t="n">
-        <v>31.38358490566043</v>
+        <v>31.35420961992052</v>
       </c>
       <c r="S18" t="n">
-        <v>9.388915094339628</v>
+        <v>9.380126994939479</v>
       </c>
       <c r="T18" t="n">
-        <v>2.03740566037736</v>
+        <v>2.035498632431968</v>
       </c>
       <c r="U18" t="n">
-        <v>0.03325471698113213</v>
+        <v>0.03322359030084825</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -32302,49 +32302,49 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4237704918032792</v>
+        <v>0.4233738392435961</v>
       </c>
       <c r="H19" t="n">
-        <v>3.767704918032794</v>
+        <v>3.764178316183975</v>
       </c>
       <c r="I19" t="n">
-        <v>12.74393442622953</v>
+        <v>12.73200600198015</v>
       </c>
       <c r="J19" t="n">
-        <v>29.96057377049184</v>
+        <v>29.93253043452224</v>
       </c>
       <c r="K19" t="n">
-        <v>49.23442622950824</v>
+        <v>49.18834241393778</v>
       </c>
       <c r="L19" t="n">
-        <v>63.00311475409845</v>
+        <v>62.94414333627064</v>
       </c>
       <c r="M19" t="n">
-        <v>66.4279508196722</v>
+        <v>66.36577372797569</v>
       </c>
       <c r="N19" t="n">
-        <v>64.84844262295094</v>
+        <v>64.78774396352233</v>
       </c>
       <c r="O19" t="n">
-        <v>59.89803278688535</v>
+        <v>59.84196775054031</v>
       </c>
       <c r="P19" t="n">
-        <v>51.25311475409841</v>
+        <v>51.20514142997091</v>
       </c>
       <c r="Q19" t="n">
-        <v>35.48500000000005</v>
+        <v>35.45178575702512</v>
       </c>
       <c r="R19" t="n">
-        <v>19.05426229508199</v>
+        <v>19.03642735362569</v>
       </c>
       <c r="S19" t="n">
-        <v>7.385163934426236</v>
+        <v>7.378251362090666</v>
       </c>
       <c r="T19" t="n">
-        <v>1.81065573770492</v>
+        <v>1.808960949495364</v>
       </c>
       <c r="U19" t="n">
-        <v>0.02311475409836071</v>
+        <v>0.02309311850419617</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -32381,49 +32381,49 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9447236180904528</v>
+        <v>0.9438393492502272</v>
       </c>
       <c r="H20" t="n">
-        <v>9.675150753768852</v>
+        <v>9.666094735508892</v>
       </c>
       <c r="I20" t="n">
-        <v>36.42145728643222</v>
+        <v>36.38736651196942</v>
       </c>
       <c r="J20" t="n">
-        <v>80.18223618090464</v>
+        <v>80.10718496842655</v>
       </c>
       <c r="K20" t="n">
-        <v>120.1723869346735</v>
+        <v>120.0599046221887</v>
       </c>
       <c r="L20" t="n">
-        <v>149.0844723618092</v>
+        <v>148.9449281068053</v>
       </c>
       <c r="M20" t="n">
-        <v>165.8852010050254</v>
+        <v>165.7299311340341</v>
       </c>
       <c r="N20" t="n">
-        <v>168.5693969849249</v>
+        <v>168.4116146850913</v>
       </c>
       <c r="O20" t="n">
-        <v>159.1753015075379</v>
+        <v>159.0263121559844</v>
       </c>
       <c r="P20" t="n">
-        <v>135.8524371859298</v>
+        <v>135.7252782213693</v>
       </c>
       <c r="Q20" t="n">
-        <v>102.0195226130655</v>
+        <v>101.9240315263455</v>
       </c>
       <c r="R20" t="n">
-        <v>59.34399497487446</v>
+        <v>59.28844852233964</v>
       </c>
       <c r="S20" t="n">
-        <v>21.52788944723622</v>
+        <v>21.50773917103957</v>
       </c>
       <c r="T20" t="n">
-        <v>4.135527638190959</v>
+        <v>4.131656751342872</v>
       </c>
       <c r="U20" t="n">
-        <v>0.07557788944723622</v>
+        <v>0.07550714794001816</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -32460,49 +32460,49 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5054716981132082</v>
+        <v>0.5049985725728932</v>
       </c>
       <c r="H21" t="n">
-        <v>4.881792452830196</v>
+        <v>4.877223056164522</v>
       </c>
       <c r="I21" t="n">
-        <v>17.40330188679248</v>
+        <v>17.38701225744391</v>
       </c>
       <c r="J21" t="n">
-        <v>47.75599056603781</v>
+        <v>47.71129057803813</v>
       </c>
       <c r="K21" t="n">
-        <v>81.62259433962275</v>
+        <v>81.54619494042197</v>
       </c>
       <c r="L21" t="n">
-        <v>109.7516509433964</v>
+        <v>109.6489225228995</v>
       </c>
       <c r="M21" t="n">
-        <v>128.0750000000002</v>
+        <v>127.9551207786668</v>
       </c>
       <c r="N21" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O21" t="n">
-        <v>120.2645754716983</v>
+        <v>120.1520068700076</v>
       </c>
       <c r="P21" t="n">
-        <v>96.52292452830203</v>
+        <v>96.43257830122204</v>
       </c>
       <c r="Q21" t="n">
-        <v>64.52301886792462</v>
+        <v>64.46262480772582</v>
       </c>
       <c r="R21" t="n">
-        <v>31.38358490566043</v>
+        <v>31.35420961992052</v>
       </c>
       <c r="S21" t="n">
-        <v>9.388915094339628</v>
+        <v>9.380126994939479</v>
       </c>
       <c r="T21" t="n">
-        <v>2.03740566037736</v>
+        <v>2.035498632431968</v>
       </c>
       <c r="U21" t="n">
-        <v>0.03325471698113213</v>
+        <v>0.03322359030084825</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -32539,49 +32539,49 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.4237704918032792</v>
+        <v>0.4233738392435961</v>
       </c>
       <c r="H22" t="n">
-        <v>3.767704918032794</v>
+        <v>3.764178316183975</v>
       </c>
       <c r="I22" t="n">
-        <v>12.74393442622953</v>
+        <v>12.73200600198015</v>
       </c>
       <c r="J22" t="n">
-        <v>29.96057377049184</v>
+        <v>29.93253043452224</v>
       </c>
       <c r="K22" t="n">
-        <v>49.23442622950824</v>
+        <v>49.18834241393778</v>
       </c>
       <c r="L22" t="n">
-        <v>63.00311475409845</v>
+        <v>62.94414333627064</v>
       </c>
       <c r="M22" t="n">
-        <v>66.4279508196722</v>
+        <v>66.36577372797569</v>
       </c>
       <c r="N22" t="n">
-        <v>64.84844262295094</v>
+        <v>64.78774396352233</v>
       </c>
       <c r="O22" t="n">
-        <v>59.89803278688535</v>
+        <v>59.84196775054031</v>
       </c>
       <c r="P22" t="n">
-        <v>51.25311475409841</v>
+        <v>51.20514142997091</v>
       </c>
       <c r="Q22" t="n">
-        <v>35.48500000000005</v>
+        <v>35.45178575702512</v>
       </c>
       <c r="R22" t="n">
-        <v>19.05426229508199</v>
+        <v>19.03642735362569</v>
       </c>
       <c r="S22" t="n">
-        <v>7.385163934426236</v>
+        <v>7.378251362090666</v>
       </c>
       <c r="T22" t="n">
-        <v>1.81065573770492</v>
+        <v>1.808960949495364</v>
       </c>
       <c r="U22" t="n">
-        <v>0.02311475409836071</v>
+        <v>0.02309311850419617</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -32618,49 +32618,49 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.9447236180904528</v>
+        <v>0.9438393492502272</v>
       </c>
       <c r="H23" t="n">
-        <v>9.675150753768852</v>
+        <v>9.666094735508892</v>
       </c>
       <c r="I23" t="n">
-        <v>36.42145728643222</v>
+        <v>36.38736651196942</v>
       </c>
       <c r="J23" t="n">
-        <v>80.18223618090464</v>
+        <v>80.10718496842655</v>
       </c>
       <c r="K23" t="n">
-        <v>120.1723869346735</v>
+        <v>120.0599046221887</v>
       </c>
       <c r="L23" t="n">
-        <v>149.0844723618092</v>
+        <v>148.9449281068053</v>
       </c>
       <c r="M23" t="n">
-        <v>165.8852010050254</v>
+        <v>165.7299311340341</v>
       </c>
       <c r="N23" t="n">
-        <v>168.5693969849249</v>
+        <v>168.4116146850913</v>
       </c>
       <c r="O23" t="n">
-        <v>159.1753015075379</v>
+        <v>159.0263121559844</v>
       </c>
       <c r="P23" t="n">
-        <v>135.8524371859298</v>
+        <v>135.7252782213693</v>
       </c>
       <c r="Q23" t="n">
-        <v>102.0195226130655</v>
+        <v>101.9240315263455</v>
       </c>
       <c r="R23" t="n">
-        <v>59.34399497487446</v>
+        <v>59.28844852233964</v>
       </c>
       <c r="S23" t="n">
-        <v>21.52788944723622</v>
+        <v>21.50773917103957</v>
       </c>
       <c r="T23" t="n">
-        <v>4.135527638190959</v>
+        <v>4.131656751342872</v>
       </c>
       <c r="U23" t="n">
-        <v>0.07557788944723622</v>
+        <v>0.07550714794001816</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -32697,49 +32697,49 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.5054716981132082</v>
+        <v>0.5049985725728932</v>
       </c>
       <c r="H24" t="n">
-        <v>4.881792452830196</v>
+        <v>4.877223056164522</v>
       </c>
       <c r="I24" t="n">
-        <v>17.40330188679248</v>
+        <v>17.38701225744391</v>
       </c>
       <c r="J24" t="n">
-        <v>47.75599056603781</v>
+        <v>47.71129057803813</v>
       </c>
       <c r="K24" t="n">
-        <v>81.62259433962275</v>
+        <v>81.54619494042197</v>
       </c>
       <c r="L24" t="n">
-        <v>109.7516509433964</v>
+        <v>109.6489225228995</v>
       </c>
       <c r="M24" t="n">
-        <v>128.0750000000002</v>
+        <v>127.9551207786668</v>
       </c>
       <c r="N24" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O24" t="n">
-        <v>120.2645754716983</v>
+        <v>120.1520068700076</v>
       </c>
       <c r="P24" t="n">
-        <v>96.52292452830203</v>
+        <v>96.43257830122204</v>
       </c>
       <c r="Q24" t="n">
-        <v>64.52301886792462</v>
+        <v>64.46262480772582</v>
       </c>
       <c r="R24" t="n">
-        <v>31.38358490566043</v>
+        <v>31.35420961992052</v>
       </c>
       <c r="S24" t="n">
-        <v>9.388915094339628</v>
+        <v>9.380126994939479</v>
       </c>
       <c r="T24" t="n">
-        <v>2.03740566037736</v>
+        <v>2.035498632431968</v>
       </c>
       <c r="U24" t="n">
-        <v>0.03325471698113213</v>
+        <v>0.03322359030084825</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -32776,49 +32776,49 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.4237704918032792</v>
+        <v>0.4233738392435961</v>
       </c>
       <c r="H25" t="n">
-        <v>3.767704918032794</v>
+        <v>3.764178316183975</v>
       </c>
       <c r="I25" t="n">
-        <v>12.74393442622953</v>
+        <v>12.73200600198015</v>
       </c>
       <c r="J25" t="n">
-        <v>29.96057377049184</v>
+        <v>29.93253043452224</v>
       </c>
       <c r="K25" t="n">
-        <v>49.23442622950824</v>
+        <v>49.18834241393778</v>
       </c>
       <c r="L25" t="n">
-        <v>63.00311475409845</v>
+        <v>62.94414333627064</v>
       </c>
       <c r="M25" t="n">
-        <v>66.4279508196722</v>
+        <v>66.36577372797569</v>
       </c>
       <c r="N25" t="n">
-        <v>64.84844262295094</v>
+        <v>64.78774396352233</v>
       </c>
       <c r="O25" t="n">
-        <v>59.89803278688535</v>
+        <v>59.84196775054031</v>
       </c>
       <c r="P25" t="n">
-        <v>51.25311475409841</v>
+        <v>51.20514142997091</v>
       </c>
       <c r="Q25" t="n">
-        <v>35.48500000000005</v>
+        <v>35.45178575702512</v>
       </c>
       <c r="R25" t="n">
-        <v>19.05426229508199</v>
+        <v>19.03642735362569</v>
       </c>
       <c r="S25" t="n">
-        <v>7.385163934426236</v>
+        <v>7.378251362090666</v>
       </c>
       <c r="T25" t="n">
-        <v>1.81065573770492</v>
+        <v>1.808960949495364</v>
       </c>
       <c r="U25" t="n">
-        <v>0.02311475409836071</v>
+        <v>0.02309311850419617</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -32855,49 +32855,49 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0.9447236180904528</v>
+        <v>0.9438393492502272</v>
       </c>
       <c r="H26" t="n">
-        <v>9.675150753768852</v>
+        <v>9.666094735508892</v>
       </c>
       <c r="I26" t="n">
-        <v>36.42145728643222</v>
+        <v>36.38736651196942</v>
       </c>
       <c r="J26" t="n">
-        <v>80.18223618090464</v>
+        <v>80.10718496842655</v>
       </c>
       <c r="K26" t="n">
-        <v>120.1723869346735</v>
+        <v>120.0599046221887</v>
       </c>
       <c r="L26" t="n">
-        <v>149.0844723618092</v>
+        <v>148.9449281068053</v>
       </c>
       <c r="M26" t="n">
-        <v>165.8852010050254</v>
+        <v>165.7299311340341</v>
       </c>
       <c r="N26" t="n">
-        <v>168.5693969849249</v>
+        <v>168.4116146850913</v>
       </c>
       <c r="O26" t="n">
-        <v>159.1753015075379</v>
+        <v>159.0263121559844</v>
       </c>
       <c r="P26" t="n">
-        <v>135.8524371859298</v>
+        <v>135.7252782213693</v>
       </c>
       <c r="Q26" t="n">
-        <v>102.0195226130655</v>
+        <v>101.9240315263455</v>
       </c>
       <c r="R26" t="n">
-        <v>59.34399497487446</v>
+        <v>59.28844852233964</v>
       </c>
       <c r="S26" t="n">
-        <v>21.52788944723622</v>
+        <v>21.50773917103957</v>
       </c>
       <c r="T26" t="n">
-        <v>4.135527638190959</v>
+        <v>4.131656751342872</v>
       </c>
       <c r="U26" t="n">
-        <v>0.07557788944723622</v>
+        <v>0.07550714794001816</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -32934,49 +32934,49 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.5054716981132082</v>
+        <v>0.5049985725728932</v>
       </c>
       <c r="H27" t="n">
-        <v>4.881792452830196</v>
+        <v>4.877223056164522</v>
       </c>
       <c r="I27" t="n">
-        <v>17.40330188679248</v>
+        <v>17.38701225744391</v>
       </c>
       <c r="J27" t="n">
-        <v>47.75599056603781</v>
+        <v>47.71129057803813</v>
       </c>
       <c r="K27" t="n">
-        <v>81.62259433962275</v>
+        <v>81.54619494042197</v>
       </c>
       <c r="L27" t="n">
-        <v>109.7516509433964</v>
+        <v>109.6489225228995</v>
       </c>
       <c r="M27" t="n">
-        <v>128.0750000000002</v>
+        <v>127.9551207786668</v>
       </c>
       <c r="N27" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O27" t="n">
-        <v>120.2645754716983</v>
+        <v>120.1520068700076</v>
       </c>
       <c r="P27" t="n">
-        <v>96.52292452830203</v>
+        <v>96.43257830122204</v>
       </c>
       <c r="Q27" t="n">
-        <v>64.52301886792462</v>
+        <v>64.46262480772582</v>
       </c>
       <c r="R27" t="n">
-        <v>31.38358490566043</v>
+        <v>31.35420961992052</v>
       </c>
       <c r="S27" t="n">
-        <v>9.388915094339628</v>
+        <v>9.380126994939479</v>
       </c>
       <c r="T27" t="n">
-        <v>2.03740566037736</v>
+        <v>2.035498632431968</v>
       </c>
       <c r="U27" t="n">
-        <v>0.03325471698113213</v>
+        <v>0.03322359030084825</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -33013,49 +33013,49 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.4237704918032792</v>
+        <v>0.4233738392435961</v>
       </c>
       <c r="H28" t="n">
-        <v>3.767704918032794</v>
+        <v>3.764178316183975</v>
       </c>
       <c r="I28" t="n">
-        <v>12.74393442622953</v>
+        <v>12.73200600198015</v>
       </c>
       <c r="J28" t="n">
-        <v>29.96057377049184</v>
+        <v>29.93253043452224</v>
       </c>
       <c r="K28" t="n">
-        <v>49.23442622950824</v>
+        <v>49.18834241393778</v>
       </c>
       <c r="L28" t="n">
-        <v>63.00311475409845</v>
+        <v>62.94414333627064</v>
       </c>
       <c r="M28" t="n">
-        <v>66.4279508196722</v>
+        <v>66.36577372797569</v>
       </c>
       <c r="N28" t="n">
-        <v>64.84844262295094</v>
+        <v>64.78774396352233</v>
       </c>
       <c r="O28" t="n">
-        <v>59.89803278688535</v>
+        <v>59.84196775054031</v>
       </c>
       <c r="P28" t="n">
-        <v>51.25311475409841</v>
+        <v>51.20514142997091</v>
       </c>
       <c r="Q28" t="n">
-        <v>35.48500000000005</v>
+        <v>35.45178575702512</v>
       </c>
       <c r="R28" t="n">
-        <v>19.05426229508199</v>
+        <v>19.03642735362569</v>
       </c>
       <c r="S28" t="n">
-        <v>7.385163934426236</v>
+        <v>7.378251362090666</v>
       </c>
       <c r="T28" t="n">
-        <v>1.81065573770492</v>
+        <v>1.808960949495364</v>
       </c>
       <c r="U28" t="n">
-        <v>0.02311475409836071</v>
+        <v>0.02309311850419617</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -33092,49 +33092,49 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.9447236180904528</v>
+        <v>0.9438393492502272</v>
       </c>
       <c r="H29" t="n">
-        <v>9.675150753768852</v>
+        <v>9.666094735508892</v>
       </c>
       <c r="I29" t="n">
-        <v>36.42145728643222</v>
+        <v>36.38736651196942</v>
       </c>
       <c r="J29" t="n">
-        <v>80.18223618090464</v>
+        <v>80.10718496842655</v>
       </c>
       <c r="K29" t="n">
-        <v>120.1723869346735</v>
+        <v>120.0599046221887</v>
       </c>
       <c r="L29" t="n">
-        <v>149.0844723618092</v>
+        <v>148.9449281068053</v>
       </c>
       <c r="M29" t="n">
-        <v>165.8852010050254</v>
+        <v>165.7299311340341</v>
       </c>
       <c r="N29" t="n">
-        <v>168.5693969849249</v>
+        <v>168.4116146850913</v>
       </c>
       <c r="O29" t="n">
-        <v>159.1753015075379</v>
+        <v>159.0263121559844</v>
       </c>
       <c r="P29" t="n">
-        <v>135.8524371859298</v>
+        <v>135.7252782213693</v>
       </c>
       <c r="Q29" t="n">
-        <v>102.0195226130655</v>
+        <v>101.9240315263455</v>
       </c>
       <c r="R29" t="n">
-        <v>59.34399497487446</v>
+        <v>59.28844852233964</v>
       </c>
       <c r="S29" t="n">
-        <v>21.52788944723622</v>
+        <v>21.50773917103957</v>
       </c>
       <c r="T29" t="n">
-        <v>4.135527638190959</v>
+        <v>4.131656751342872</v>
       </c>
       <c r="U29" t="n">
-        <v>0.07557788944723622</v>
+        <v>0.07550714794001816</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -33171,49 +33171,49 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.5054716981132082</v>
+        <v>0.5049985725728932</v>
       </c>
       <c r="H30" t="n">
-        <v>4.881792452830196</v>
+        <v>4.877223056164522</v>
       </c>
       <c r="I30" t="n">
-        <v>17.40330188679248</v>
+        <v>17.38701225744391</v>
       </c>
       <c r="J30" t="n">
-        <v>47.75599056603781</v>
+        <v>47.71129057803813</v>
       </c>
       <c r="K30" t="n">
-        <v>81.62259433962275</v>
+        <v>81.54619494042197</v>
       </c>
       <c r="L30" t="n">
-        <v>109.7516509433964</v>
+        <v>109.6489225228995</v>
       </c>
       <c r="M30" t="n">
-        <v>128.0750000000002</v>
+        <v>127.9551207786668</v>
       </c>
       <c r="N30" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O30" t="n">
-        <v>120.2645754716983</v>
+        <v>120.1520068700076</v>
       </c>
       <c r="P30" t="n">
-        <v>96.52292452830203</v>
+        <v>96.43257830122204</v>
       </c>
       <c r="Q30" t="n">
-        <v>64.52301886792462</v>
+        <v>64.46262480772582</v>
       </c>
       <c r="R30" t="n">
-        <v>31.38358490566043</v>
+        <v>31.35420961992052</v>
       </c>
       <c r="S30" t="n">
-        <v>9.388915094339628</v>
+        <v>9.380126994939479</v>
       </c>
       <c r="T30" t="n">
-        <v>2.03740566037736</v>
+        <v>2.035498632431968</v>
       </c>
       <c r="U30" t="n">
-        <v>0.03325471698113213</v>
+        <v>0.03322359030084825</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -33250,49 +33250,49 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.4237704918032792</v>
+        <v>0.4233738392435961</v>
       </c>
       <c r="H31" t="n">
-        <v>3.767704918032794</v>
+        <v>3.764178316183975</v>
       </c>
       <c r="I31" t="n">
-        <v>12.74393442622953</v>
+        <v>12.73200600198015</v>
       </c>
       <c r="J31" t="n">
-        <v>29.96057377049184</v>
+        <v>29.93253043452224</v>
       </c>
       <c r="K31" t="n">
-        <v>49.23442622950824</v>
+        <v>49.18834241393778</v>
       </c>
       <c r="L31" t="n">
-        <v>63.00311475409845</v>
+        <v>62.94414333627064</v>
       </c>
       <c r="M31" t="n">
-        <v>66.4279508196722</v>
+        <v>66.36577372797569</v>
       </c>
       <c r="N31" t="n">
-        <v>64.84844262295094</v>
+        <v>64.78774396352233</v>
       </c>
       <c r="O31" t="n">
-        <v>59.89803278688535</v>
+        <v>59.84196775054031</v>
       </c>
       <c r="P31" t="n">
-        <v>51.25311475409841</v>
+        <v>51.20514142997091</v>
       </c>
       <c r="Q31" t="n">
-        <v>35.48500000000005</v>
+        <v>35.45178575702512</v>
       </c>
       <c r="R31" t="n">
-        <v>19.05426229508199</v>
+        <v>19.03642735362569</v>
       </c>
       <c r="S31" t="n">
-        <v>7.385163934426236</v>
+        <v>7.378251362090666</v>
       </c>
       <c r="T31" t="n">
-        <v>1.81065573770492</v>
+        <v>1.808960949495364</v>
       </c>
       <c r="U31" t="n">
-        <v>0.02311475409836071</v>
+        <v>0.02309311850419617</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -33329,49 +33329,49 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.9447236180904528</v>
+        <v>0.9438393492502272</v>
       </c>
       <c r="H32" t="n">
-        <v>9.675150753768852</v>
+        <v>9.666094735508892</v>
       </c>
       <c r="I32" t="n">
-        <v>36.42145728643222</v>
+        <v>36.38736651196942</v>
       </c>
       <c r="J32" t="n">
-        <v>80.18223618090464</v>
+        <v>80.10718496842655</v>
       </c>
       <c r="K32" t="n">
-        <v>120.1723869346735</v>
+        <v>120.0599046221887</v>
       </c>
       <c r="L32" t="n">
-        <v>149.0844723618092</v>
+        <v>148.9449281068054</v>
       </c>
       <c r="M32" t="n">
-        <v>165.8852010050254</v>
+        <v>165.7299311340341</v>
       </c>
       <c r="N32" t="n">
-        <v>168.5693969849249</v>
+        <v>168.4116146850913</v>
       </c>
       <c r="O32" t="n">
-        <v>159.1753015075379</v>
+        <v>159.0263121559843</v>
       </c>
       <c r="P32" t="n">
-        <v>135.8524371859298</v>
+        <v>135.7252782213693</v>
       </c>
       <c r="Q32" t="n">
-        <v>102.0195226130655</v>
+        <v>101.9240315263455</v>
       </c>
       <c r="R32" t="n">
-        <v>59.34399497487446</v>
+        <v>59.28844852233964</v>
       </c>
       <c r="S32" t="n">
-        <v>21.52788944723622</v>
+        <v>21.50773917103957</v>
       </c>
       <c r="T32" t="n">
-        <v>4.135527638190959</v>
+        <v>4.131656751342871</v>
       </c>
       <c r="U32" t="n">
-        <v>0.07557788944723622</v>
+        <v>0.07550714794001816</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -33408,49 +33408,49 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.5054716981132082</v>
+        <v>0.5049985725728932</v>
       </c>
       <c r="H33" t="n">
-        <v>4.881792452830196</v>
+        <v>4.877223056164522</v>
       </c>
       <c r="I33" t="n">
-        <v>17.40330188679248</v>
+        <v>17.38701225744391</v>
       </c>
       <c r="J33" t="n">
-        <v>47.75599056603781</v>
+        <v>47.71129057803813</v>
       </c>
       <c r="K33" t="n">
-        <v>81.62259433962275</v>
+        <v>81.54619494042197</v>
       </c>
       <c r="L33" t="n">
-        <v>109.7516509433964</v>
+        <v>109.6489225228995</v>
       </c>
       <c r="M33" t="n">
-        <v>128.0750000000002</v>
+        <v>127.9551207786668</v>
       </c>
       <c r="N33" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O33" t="n">
-        <v>120.2645754716983</v>
+        <v>120.1520068700076</v>
       </c>
       <c r="P33" t="n">
-        <v>96.52292452830203</v>
+        <v>96.43257830122204</v>
       </c>
       <c r="Q33" t="n">
-        <v>64.52301886792462</v>
+        <v>64.4626248077258</v>
       </c>
       <c r="R33" t="n">
-        <v>31.38358490566043</v>
+        <v>31.35420961992052</v>
       </c>
       <c r="S33" t="n">
-        <v>9.388915094339628</v>
+        <v>9.380126994939479</v>
       </c>
       <c r="T33" t="n">
-        <v>2.03740566037736</v>
+        <v>2.035498632431968</v>
       </c>
       <c r="U33" t="n">
-        <v>0.03325471698113213</v>
+        <v>0.03322359030084825</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -33487,49 +33487,49 @@
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.4237704918032792</v>
+        <v>0.423373839243596</v>
       </c>
       <c r="H34" t="n">
-        <v>3.767704918032794</v>
+        <v>3.764178316183975</v>
       </c>
       <c r="I34" t="n">
-        <v>12.74393442622953</v>
+        <v>12.73200600198015</v>
       </c>
       <c r="J34" t="n">
-        <v>29.96057377049184</v>
+        <v>29.93253043452224</v>
       </c>
       <c r="K34" t="n">
-        <v>49.23442622950824</v>
+        <v>49.18834241393778</v>
       </c>
       <c r="L34" t="n">
-        <v>63.00311475409845</v>
+        <v>62.94414333627064</v>
       </c>
       <c r="M34" t="n">
-        <v>66.4279508196722</v>
+        <v>66.36577372797568</v>
       </c>
       <c r="N34" t="n">
-        <v>64.84844262295094</v>
+        <v>64.78774396352233</v>
       </c>
       <c r="O34" t="n">
-        <v>59.89803278688535</v>
+        <v>59.84196775054031</v>
       </c>
       <c r="P34" t="n">
-        <v>51.25311475409841</v>
+        <v>51.20514142997091</v>
       </c>
       <c r="Q34" t="n">
-        <v>35.48500000000005</v>
+        <v>35.45178575702513</v>
       </c>
       <c r="R34" t="n">
-        <v>19.05426229508199</v>
+        <v>19.03642735362569</v>
       </c>
       <c r="S34" t="n">
-        <v>7.385163934426236</v>
+        <v>7.378251362090667</v>
       </c>
       <c r="T34" t="n">
-        <v>1.81065573770492</v>
+        <v>1.808960949495364</v>
       </c>
       <c r="U34" t="n">
-        <v>0.02311475409836071</v>
+        <v>0.02309311850419617</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -33566,49 +33566,49 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>0.9447236180904528</v>
+        <v>0.9438393492502272</v>
       </c>
       <c r="H35" t="n">
-        <v>9.675150753768852</v>
+        <v>9.666094735508892</v>
       </c>
       <c r="I35" t="n">
-        <v>36.42145728643222</v>
+        <v>36.38736651196942</v>
       </c>
       <c r="J35" t="n">
-        <v>80.18223618090464</v>
+        <v>80.10718496842655</v>
       </c>
       <c r="K35" t="n">
-        <v>120.1723869346735</v>
+        <v>120.0599046221887</v>
       </c>
       <c r="L35" t="n">
-        <v>149.0844723618092</v>
+        <v>148.9449281068053</v>
       </c>
       <c r="M35" t="n">
-        <v>165.8852010050254</v>
+        <v>165.7299311340341</v>
       </c>
       <c r="N35" t="n">
-        <v>168.5693969849249</v>
+        <v>168.4116146850913</v>
       </c>
       <c r="O35" t="n">
-        <v>159.1753015075379</v>
+        <v>159.0263121559844</v>
       </c>
       <c r="P35" t="n">
-        <v>135.8524371859298</v>
+        <v>135.7252782213693</v>
       </c>
       <c r="Q35" t="n">
-        <v>102.0195226130655</v>
+        <v>101.9240315263455</v>
       </c>
       <c r="R35" t="n">
-        <v>59.34399497487446</v>
+        <v>59.28844852233964</v>
       </c>
       <c r="S35" t="n">
-        <v>21.52788944723622</v>
+        <v>21.50773917103957</v>
       </c>
       <c r="T35" t="n">
-        <v>4.135527638190959</v>
+        <v>4.131656751342872</v>
       </c>
       <c r="U35" t="n">
-        <v>0.07557788944723622</v>
+        <v>0.07550714794001816</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -33645,49 +33645,49 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0.5054716981132082</v>
+        <v>0.5049985725728932</v>
       </c>
       <c r="H36" t="n">
-        <v>4.881792452830196</v>
+        <v>4.877223056164522</v>
       </c>
       <c r="I36" t="n">
-        <v>17.40330188679248</v>
+        <v>17.38701225744391</v>
       </c>
       <c r="J36" t="n">
-        <v>47.75599056603781</v>
+        <v>47.71129057803813</v>
       </c>
       <c r="K36" t="n">
-        <v>81.62259433962275</v>
+        <v>81.54619494042197</v>
       </c>
       <c r="L36" t="n">
-        <v>109.7516509433964</v>
+        <v>109.6489225228995</v>
       </c>
       <c r="M36" t="n">
-        <v>128.0750000000002</v>
+        <v>127.9551207786668</v>
       </c>
       <c r="N36" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O36" t="n">
-        <v>120.2645754716983</v>
+        <v>120.1520068700076</v>
       </c>
       <c r="P36" t="n">
-        <v>96.52292452830203</v>
+        <v>96.43257830122204</v>
       </c>
       <c r="Q36" t="n">
-        <v>64.52301886792462</v>
+        <v>64.46262480772582</v>
       </c>
       <c r="R36" t="n">
-        <v>31.38358490566043</v>
+        <v>31.35420961992052</v>
       </c>
       <c r="S36" t="n">
-        <v>9.388915094339628</v>
+        <v>9.380126994939479</v>
       </c>
       <c r="T36" t="n">
-        <v>2.03740566037736</v>
+        <v>2.035498632431968</v>
       </c>
       <c r="U36" t="n">
-        <v>0.03325471698113213</v>
+        <v>0.03322359030084825</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -33724,49 +33724,49 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0.4237704918032792</v>
+        <v>0.4233738392435961</v>
       </c>
       <c r="H37" t="n">
-        <v>3.767704918032794</v>
+        <v>3.764178316183975</v>
       </c>
       <c r="I37" t="n">
-        <v>12.74393442622953</v>
+        <v>12.73200600198015</v>
       </c>
       <c r="J37" t="n">
-        <v>29.96057377049184</v>
+        <v>29.93253043452224</v>
       </c>
       <c r="K37" t="n">
-        <v>49.23442622950824</v>
+        <v>49.18834241393778</v>
       </c>
       <c r="L37" t="n">
-        <v>63.00311475409845</v>
+        <v>62.94414333627064</v>
       </c>
       <c r="M37" t="n">
-        <v>66.4279508196722</v>
+        <v>66.36577372797569</v>
       </c>
       <c r="N37" t="n">
-        <v>64.84844262295094</v>
+        <v>64.78774396352233</v>
       </c>
       <c r="O37" t="n">
-        <v>59.89803278688535</v>
+        <v>59.84196775054031</v>
       </c>
       <c r="P37" t="n">
-        <v>51.25311475409841</v>
+        <v>51.20514142997091</v>
       </c>
       <c r="Q37" t="n">
-        <v>35.48500000000005</v>
+        <v>35.45178575702512</v>
       </c>
       <c r="R37" t="n">
-        <v>19.05426229508199</v>
+        <v>19.03642735362569</v>
       </c>
       <c r="S37" t="n">
-        <v>7.385163934426236</v>
+        <v>7.378251362090666</v>
       </c>
       <c r="T37" t="n">
-        <v>1.81065573770492</v>
+        <v>1.808960949495364</v>
       </c>
       <c r="U37" t="n">
-        <v>0.02311475409836071</v>
+        <v>0.02309311850419617</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -33803,49 +33803,49 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0.9447236180904528</v>
+        <v>0.9438393492502272</v>
       </c>
       <c r="H38" t="n">
-        <v>9.675150753768852</v>
+        <v>9.666094735508892</v>
       </c>
       <c r="I38" t="n">
-        <v>36.42145728643222</v>
+        <v>36.38736651196942</v>
       </c>
       <c r="J38" t="n">
-        <v>80.18223618090464</v>
+        <v>80.10718496842655</v>
       </c>
       <c r="K38" t="n">
-        <v>120.1723869346735</v>
+        <v>120.0599046221887</v>
       </c>
       <c r="L38" t="n">
-        <v>149.0844723618092</v>
+        <v>148.9449281068053</v>
       </c>
       <c r="M38" t="n">
-        <v>165.8852010050254</v>
+        <v>165.7299311340341</v>
       </c>
       <c r="N38" t="n">
-        <v>168.5693969849249</v>
+        <v>168.4116146850913</v>
       </c>
       <c r="O38" t="n">
-        <v>159.1753015075379</v>
+        <v>159.0263121559844</v>
       </c>
       <c r="P38" t="n">
-        <v>135.8524371859298</v>
+        <v>135.7252782213693</v>
       </c>
       <c r="Q38" t="n">
-        <v>102.0195226130655</v>
+        <v>101.9240315263455</v>
       </c>
       <c r="R38" t="n">
-        <v>59.34399497487446</v>
+        <v>59.28844852233964</v>
       </c>
       <c r="S38" t="n">
-        <v>21.52788944723622</v>
+        <v>21.50773917103957</v>
       </c>
       <c r="T38" t="n">
-        <v>4.135527638190959</v>
+        <v>4.131656751342872</v>
       </c>
       <c r="U38" t="n">
-        <v>0.07557788944723622</v>
+        <v>0.07550714794001816</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -33882,49 +33882,49 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0.5054716981132082</v>
+        <v>0.5049985725728932</v>
       </c>
       <c r="H39" t="n">
-        <v>4.881792452830196</v>
+        <v>4.877223056164522</v>
       </c>
       <c r="I39" t="n">
-        <v>17.40330188679248</v>
+        <v>17.38701225744391</v>
       </c>
       <c r="J39" t="n">
-        <v>47.75599056603781</v>
+        <v>47.71129057803813</v>
       </c>
       <c r="K39" t="n">
-        <v>81.62259433962275</v>
+        <v>81.54619494042197</v>
       </c>
       <c r="L39" t="n">
-        <v>109.7516509433964</v>
+        <v>109.6489225228995</v>
       </c>
       <c r="M39" t="n">
-        <v>128.0750000000002</v>
+        <v>127.9551207786668</v>
       </c>
       <c r="N39" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O39" t="n">
-        <v>120.2645754716983</v>
+        <v>120.1520068700076</v>
       </c>
       <c r="P39" t="n">
-        <v>96.52292452830203</v>
+        <v>96.43257830122204</v>
       </c>
       <c r="Q39" t="n">
-        <v>64.52301886792462</v>
+        <v>64.46262480772582</v>
       </c>
       <c r="R39" t="n">
-        <v>31.38358490566043</v>
+        <v>31.35420961992052</v>
       </c>
       <c r="S39" t="n">
-        <v>9.388915094339628</v>
+        <v>9.380126994939479</v>
       </c>
       <c r="T39" t="n">
-        <v>2.03740566037736</v>
+        <v>2.035498632431968</v>
       </c>
       <c r="U39" t="n">
-        <v>0.03325471698113213</v>
+        <v>0.03322359030084825</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -33961,49 +33961,49 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0.4237704918032792</v>
+        <v>0.4233738392435961</v>
       </c>
       <c r="H40" t="n">
-        <v>3.767704918032794</v>
+        <v>3.764178316183975</v>
       </c>
       <c r="I40" t="n">
-        <v>12.74393442622953</v>
+        <v>12.73200600198015</v>
       </c>
       <c r="J40" t="n">
-        <v>29.96057377049184</v>
+        <v>29.93253043452224</v>
       </c>
       <c r="K40" t="n">
-        <v>49.23442622950824</v>
+        <v>49.18834241393778</v>
       </c>
       <c r="L40" t="n">
-        <v>63.00311475409845</v>
+        <v>62.94414333627064</v>
       </c>
       <c r="M40" t="n">
-        <v>66.4279508196722</v>
+        <v>66.36577372797569</v>
       </c>
       <c r="N40" t="n">
-        <v>64.84844262295094</v>
+        <v>64.78774396352233</v>
       </c>
       <c r="O40" t="n">
-        <v>59.89803278688535</v>
+        <v>59.84196775054031</v>
       </c>
       <c r="P40" t="n">
-        <v>51.25311475409841</v>
+        <v>51.20514142997091</v>
       </c>
       <c r="Q40" t="n">
-        <v>35.48500000000005</v>
+        <v>35.45178575702512</v>
       </c>
       <c r="R40" t="n">
-        <v>19.05426229508199</v>
+        <v>19.03642735362569</v>
       </c>
       <c r="S40" t="n">
-        <v>7.385163934426236</v>
+        <v>7.378251362090666</v>
       </c>
       <c r="T40" t="n">
-        <v>1.81065573770492</v>
+        <v>1.808960949495364</v>
       </c>
       <c r="U40" t="n">
-        <v>0.02311475409836071</v>
+        <v>0.02309311850419617</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -34040,49 +34040,49 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0.9447236180904528</v>
+        <v>0.9438393492502272</v>
       </c>
       <c r="H41" t="n">
-        <v>9.675150753768852</v>
+        <v>9.666094735508892</v>
       </c>
       <c r="I41" t="n">
-        <v>36.42145728643222</v>
+        <v>36.38736651196942</v>
       </c>
       <c r="J41" t="n">
-        <v>80.18223618090465</v>
+        <v>80.10718496842655</v>
       </c>
       <c r="K41" t="n">
-        <v>120.1723869346735</v>
+        <v>120.0599046221887</v>
       </c>
       <c r="L41" t="n">
-        <v>149.0844723618092</v>
+        <v>148.9449281068053</v>
       </c>
       <c r="M41" t="n">
-        <v>165.8852010050254</v>
+        <v>165.7299311340341</v>
       </c>
       <c r="N41" t="n">
-        <v>168.5693969849249</v>
+        <v>168.4116146850913</v>
       </c>
       <c r="O41" t="n">
-        <v>159.1753015075379</v>
+        <v>159.0263121559844</v>
       </c>
       <c r="P41" t="n">
-        <v>135.8524371859298</v>
+        <v>135.7252782213693</v>
       </c>
       <c r="Q41" t="n">
-        <v>102.0195226130655</v>
+        <v>101.9240315263455</v>
       </c>
       <c r="R41" t="n">
-        <v>59.34399497487446</v>
+        <v>59.28844852233964</v>
       </c>
       <c r="S41" t="n">
-        <v>21.52788944723622</v>
+        <v>21.50773917103957</v>
       </c>
       <c r="T41" t="n">
-        <v>4.135527638190959</v>
+        <v>4.131656751342872</v>
       </c>
       <c r="U41" t="n">
-        <v>0.07557788944723622</v>
+        <v>0.07550714794001816</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -34119,49 +34119,49 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0.5054716981132082</v>
+        <v>0.5049985725728932</v>
       </c>
       <c r="H42" t="n">
-        <v>4.881792452830195</v>
+        <v>4.877223056164522</v>
       </c>
       <c r="I42" t="n">
-        <v>17.40330188679248</v>
+        <v>17.38701225744391</v>
       </c>
       <c r="J42" t="n">
-        <v>47.7559905660378</v>
+        <v>47.71129057803813</v>
       </c>
       <c r="K42" t="n">
-        <v>81.62259433962275</v>
+        <v>81.54619494042197</v>
       </c>
       <c r="L42" t="n">
-        <v>109.7516509433964</v>
+        <v>109.6489225228995</v>
       </c>
       <c r="M42" t="n">
-        <v>128.0750000000002</v>
+        <v>127.9551207786668</v>
       </c>
       <c r="N42" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O42" t="n">
-        <v>120.2645754716983</v>
+        <v>120.1520068700076</v>
       </c>
       <c r="P42" t="n">
-        <v>96.52292452830203</v>
+        <v>96.43257830122204</v>
       </c>
       <c r="Q42" t="n">
-        <v>64.52301886792462</v>
+        <v>64.46262480772582</v>
       </c>
       <c r="R42" t="n">
-        <v>31.38358490566043</v>
+        <v>31.35420961992052</v>
       </c>
       <c r="S42" t="n">
-        <v>9.388915094339628</v>
+        <v>9.380126994939479</v>
       </c>
       <c r="T42" t="n">
-        <v>2.03740566037736</v>
+        <v>2.035498632431968</v>
       </c>
       <c r="U42" t="n">
-        <v>0.03325471698113213</v>
+        <v>0.03322359030084825</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -34198,49 +34198,49 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0.4237704918032792</v>
+        <v>0.4233738392435961</v>
       </c>
       <c r="H43" t="n">
-        <v>3.767704918032794</v>
+        <v>3.764178316183975</v>
       </c>
       <c r="I43" t="n">
-        <v>12.74393442622953</v>
+        <v>12.73200600198015</v>
       </c>
       <c r="J43" t="n">
-        <v>29.96057377049184</v>
+        <v>29.93253043452224</v>
       </c>
       <c r="K43" t="n">
-        <v>49.23442622950824</v>
+        <v>49.18834241393778</v>
       </c>
       <c r="L43" t="n">
-        <v>63.00311475409845</v>
+        <v>62.94414333627064</v>
       </c>
       <c r="M43" t="n">
-        <v>66.4279508196722</v>
+        <v>66.36577372797569</v>
       </c>
       <c r="N43" t="n">
-        <v>64.84844262295094</v>
+        <v>64.78774396352233</v>
       </c>
       <c r="O43" t="n">
-        <v>59.89803278688535</v>
+        <v>59.84196775054031</v>
       </c>
       <c r="P43" t="n">
-        <v>51.2531147540984</v>
+        <v>51.20514142997091</v>
       </c>
       <c r="Q43" t="n">
-        <v>35.48500000000004</v>
+        <v>35.45178575702512</v>
       </c>
       <c r="R43" t="n">
-        <v>19.05426229508198</v>
+        <v>19.03642735362569</v>
       </c>
       <c r="S43" t="n">
-        <v>7.385163934426236</v>
+        <v>7.378251362090666</v>
       </c>
       <c r="T43" t="n">
-        <v>1.81065573770492</v>
+        <v>1.808960949495364</v>
       </c>
       <c r="U43" t="n">
-        <v>0.02311475409836071</v>
+        <v>0.02309311850419617</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -34277,49 +34277,49 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0.9447236180904528</v>
+        <v>0.9438393492502272</v>
       </c>
       <c r="H44" t="n">
-        <v>9.675150753768852</v>
+        <v>9.666094735508892</v>
       </c>
       <c r="I44" t="n">
-        <v>36.42145728643222</v>
+        <v>36.38736651196942</v>
       </c>
       <c r="J44" t="n">
-        <v>80.18223618090464</v>
+        <v>80.10718496842655</v>
       </c>
       <c r="K44" t="n">
-        <v>120.1723869346735</v>
+        <v>120.0599046221887</v>
       </c>
       <c r="L44" t="n">
-        <v>149.0844723618092</v>
+        <v>148.9449281068053</v>
       </c>
       <c r="M44" t="n">
-        <v>165.8852010050254</v>
+        <v>165.7299311340341</v>
       </c>
       <c r="N44" t="n">
-        <v>168.5693969849249</v>
+        <v>168.4116146850913</v>
       </c>
       <c r="O44" t="n">
-        <v>159.1753015075379</v>
+        <v>159.0263121559844</v>
       </c>
       <c r="P44" t="n">
-        <v>135.8524371859298</v>
+        <v>135.7252782213693</v>
       </c>
       <c r="Q44" t="n">
-        <v>102.0195226130655</v>
+        <v>101.9240315263455</v>
       </c>
       <c r="R44" t="n">
-        <v>59.34399497487446</v>
+        <v>59.28844852233964</v>
       </c>
       <c r="S44" t="n">
-        <v>21.52788944723622</v>
+        <v>21.50773917103957</v>
       </c>
       <c r="T44" t="n">
-        <v>4.135527638190959</v>
+        <v>4.131656751342872</v>
       </c>
       <c r="U44" t="n">
-        <v>0.07557788944723622</v>
+        <v>0.07550714794001816</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -34356,49 +34356,49 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0.5054716981132082</v>
+        <v>0.5049985725728932</v>
       </c>
       <c r="H45" t="n">
-        <v>4.881792452830196</v>
+        <v>4.877223056164522</v>
       </c>
       <c r="I45" t="n">
-        <v>17.40330188679248</v>
+        <v>17.38701225744391</v>
       </c>
       <c r="J45" t="n">
-        <v>47.75599056603781</v>
+        <v>47.71129057803813</v>
       </c>
       <c r="K45" t="n">
-        <v>81.62259433962275</v>
+        <v>81.54619494042197</v>
       </c>
       <c r="L45" t="n">
-        <v>109.7516509433964</v>
+        <v>109.6489225228995</v>
       </c>
       <c r="M45" t="n">
-        <v>128.0750000000002</v>
+        <v>127.9551207786668</v>
       </c>
       <c r="N45" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O45" t="n">
-        <v>120.2645754716983</v>
+        <v>120.1520068700076</v>
       </c>
       <c r="P45" t="n">
-        <v>96.52292452830203</v>
+        <v>96.43257830122204</v>
       </c>
       <c r="Q45" t="n">
-        <v>64.52301886792462</v>
+        <v>64.46262480772582</v>
       </c>
       <c r="R45" t="n">
-        <v>31.38358490566043</v>
+        <v>31.35420961992052</v>
       </c>
       <c r="S45" t="n">
-        <v>9.388915094339628</v>
+        <v>9.380126994939479</v>
       </c>
       <c r="T45" t="n">
-        <v>2.03740566037736</v>
+        <v>2.035498632431968</v>
       </c>
       <c r="U45" t="n">
-        <v>0.03325471698113213</v>
+        <v>0.03322359030084825</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -34435,49 +34435,49 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>0.4237704918032792</v>
+        <v>0.4233738392435961</v>
       </c>
       <c r="H46" t="n">
-        <v>3.767704918032794</v>
+        <v>3.764178316183975</v>
       </c>
       <c r="I46" t="n">
-        <v>12.74393442622953</v>
+        <v>12.73200600198015</v>
       </c>
       <c r="J46" t="n">
-        <v>29.96057377049184</v>
+        <v>29.93253043452224</v>
       </c>
       <c r="K46" t="n">
-        <v>49.23442622950824</v>
+        <v>49.18834241393778</v>
       </c>
       <c r="L46" t="n">
-        <v>63.00311475409845</v>
+        <v>62.94414333627064</v>
       </c>
       <c r="M46" t="n">
-        <v>66.4279508196722</v>
+        <v>66.36577372797569</v>
       </c>
       <c r="N46" t="n">
-        <v>64.84844262295094</v>
+        <v>64.78774396352233</v>
       </c>
       <c r="O46" t="n">
-        <v>59.89803278688535</v>
+        <v>59.84196775054031</v>
       </c>
       <c r="P46" t="n">
-        <v>51.25311475409841</v>
+        <v>51.20514142997091</v>
       </c>
       <c r="Q46" t="n">
-        <v>35.48500000000005</v>
+        <v>35.45178575702512</v>
       </c>
       <c r="R46" t="n">
-        <v>19.05426229508199</v>
+        <v>19.03642735362569</v>
       </c>
       <c r="S46" t="n">
-        <v>7.385163934426236</v>
+        <v>7.378251362090666</v>
       </c>
       <c r="T46" t="n">
-        <v>1.81065573770492</v>
+        <v>1.808960949495364</v>
       </c>
       <c r="U46" t="n">
-        <v>0.02311475409836071</v>
+        <v>0.02309311850419617</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
